--- a/services/opengsync-app/static/resources/templates/library_prep/QUANTSEQ.xlsx
+++ b/services/opengsync-app/static/resources/templates/library_prep/QUANTSEQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hriegler\Documents\limbless-app\services\opengsync-app\static\resources\templates\library_prep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D78CB6-0E87-4367-8889-42A3130E5097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE10C98-E562-4300-A01B-CF974E7BEC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{B38823E2-9AAF-4849-A302-784C5AB9E0F5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{B38823E2-9AAF-4849-A302-784C5AB9E0F5}"/>
   </bookViews>
   <sheets>
     <sheet name="prep_table" sheetId="27" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="165">
   <si>
     <t>RIN</t>
   </si>
@@ -639,9 +639,6 @@
   </si>
   <si>
     <t>Carina Suete</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Volume for 12 samples</t>
   </si>
   <si>
     <t>pool</t>
@@ -1653,24 +1650,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1729,6 +1717,216 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1765,215 +1963,14 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4900,26 +4897,26 @@
   <dimension ref="A1:AB98"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="94" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.42578125" style="94" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="94" customWidth="1"/>
-    <col min="5" max="7" width="13.42578125" style="94" customWidth="1"/>
-    <col min="8" max="9" width="12.42578125" style="94" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" style="94" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="94" customWidth="1"/>
-    <col min="12" max="13" width="12.42578125" style="94" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" style="94" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="95"/>
-    <col min="16" max="16" width="9.85546875" style="96" customWidth="1"/>
-    <col min="17" max="17" width="7.85546875" style="94" customWidth="1"/>
-    <col min="18" max="20" width="12.42578125" style="94" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" style="94" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" style="94" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.42578125" style="94" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.140625" style="94" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="94" customWidth="1"/>
-    <col min="26" max="28" width="7.85546875" style="94" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="94"/>
+    <col min="1" max="1" width="12.42578125" style="91" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.42578125" style="91" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="91" customWidth="1"/>
+    <col min="5" max="7" width="13.42578125" style="91" customWidth="1"/>
+    <col min="8" max="9" width="12.42578125" style="91" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" style="91" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="91" customWidth="1"/>
+    <col min="12" max="13" width="12.42578125" style="91" customWidth="1"/>
+    <col min="14" max="14" width="7.85546875" style="91" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="92"/>
+    <col min="16" max="16" width="9.85546875" style="93" customWidth="1"/>
+    <col min="17" max="17" width="7.85546875" style="91" customWidth="1"/>
+    <col min="18" max="20" width="12.42578125" style="91" customWidth="1"/>
+    <col min="21" max="21" width="12.42578125" style="91" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" style="91" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.42578125" style="91" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.140625" style="91" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="91" customWidth="1"/>
+    <col min="26" max="28" width="7.85546875" style="91" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="91"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -4939,10 +4936,10 @@
         <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>90</v>
@@ -4996,7 +4993,7 @@
         <v>103</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>104</v>
@@ -5009,14 +5006,14 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="94">
+      <c r="A2" s="91">
         <v>1</v>
       </c>
-      <c r="L2" s="94" t="e">
+      <c r="L2" s="91" t="e">
         <f>I2/J2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N2" s="94">
+      <c r="N2" s="91">
         <f>5-O2</f>
         <v>0</v>
       </c>
@@ -5027,24 +5024,24 @@
         <f>+#REF!*O2</f>
         <v>#REF!</v>
       </c>
-      <c r="AA2" s="97" t="e">
+      <c r="AA2" s="94" t="e">
         <f>+MAX($Y$2:$Y$97)/Y2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2" s="97" t="e">
+      <c r="AB2" s="94" t="e">
         <f>AA2</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="94">
+      <c r="A3" s="91">
         <v>2</v>
       </c>
-      <c r="L3" s="94" t="e">
+      <c r="L3" s="91" t="e">
         <f t="shared" ref="L3:L66" si="0">I3/J3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N3" s="94">
+      <c r="N3" s="91">
         <f t="shared" ref="N3:N66" si="1">5-O3</f>
         <v>0</v>
       </c>
@@ -5055,24 +5052,24 @@
         <f>+#REF!*O3</f>
         <v>#REF!</v>
       </c>
-      <c r="AA3" s="97" t="e">
+      <c r="AA3" s="94" t="e">
         <f t="shared" ref="AA3:AA66" si="2">+MAX($Y$2:$Y$97)/Y3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB3" s="97" t="e">
+      <c r="AB3" s="94" t="e">
         <f t="shared" ref="AB3:AB66" si="3">AA3</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="94">
+      <c r="A4" s="91">
         <v>3</v>
       </c>
-      <c r="L4" s="94" t="e">
+      <c r="L4" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N4" s="94">
+      <c r="N4" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5083,24 +5080,24 @@
         <f>+#REF!*O4</f>
         <v>#REF!</v>
       </c>
-      <c r="AA4" s="97" t="e">
+      <c r="AA4" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB4" s="97" t="e">
+      <c r="AB4" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="94">
+      <c r="A5" s="91">
         <v>4</v>
       </c>
-      <c r="L5" s="94" t="e">
+      <c r="L5" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N5" s="94">
+      <c r="N5" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5111,24 +5108,24 @@
         <f>+#REF!*O5</f>
         <v>#REF!</v>
       </c>
-      <c r="AA5" s="97" t="e">
+      <c r="AA5" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB5" s="97" t="e">
+      <c r="AB5" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="94">
-        <v>5</v>
-      </c>
-      <c r="L6" s="94" t="e">
+      <c r="A6" s="91">
+        <v>5</v>
+      </c>
+      <c r="L6" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N6" s="94">
+      <c r="N6" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5139,24 +5136,24 @@
         <f>+#REF!*O6</f>
         <v>#REF!</v>
       </c>
-      <c r="AA6" s="97" t="e">
+      <c r="AA6" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB6" s="97" t="e">
+      <c r="AB6" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="94">
+      <c r="A7" s="91">
         <v>6</v>
       </c>
-      <c r="L7" s="94" t="e">
+      <c r="L7" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N7" s="94">
+      <c r="N7" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5167,24 +5164,24 @@
         <f>+#REF!*O7</f>
         <v>#REF!</v>
       </c>
-      <c r="AA7" s="97" t="e">
+      <c r="AA7" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB7" s="97" t="e">
+      <c r="AB7" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="94">
+      <c r="A8" s="91">
         <v>7</v>
       </c>
-      <c r="L8" s="94" t="e">
+      <c r="L8" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N8" s="94">
+      <c r="N8" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5195,24 +5192,24 @@
         <f>+#REF!*O8</f>
         <v>#REF!</v>
       </c>
-      <c r="AA8" s="97" t="e">
+      <c r="AA8" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB8" s="97" t="e">
+      <c r="AB8" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="94">
+      <c r="A9" s="91">
         <v>8</v>
       </c>
-      <c r="L9" s="94" t="e">
+      <c r="L9" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5223,24 +5220,24 @@
         <f>+#REF!*O9</f>
         <v>#REF!</v>
       </c>
-      <c r="AA9" s="97" t="e">
+      <c r="AA9" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB9" s="97" t="e">
+      <c r="AB9" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="94">
+      <c r="A10" s="91">
         <v>9</v>
       </c>
-      <c r="L10" s="94" t="e">
+      <c r="L10" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N10" s="94">
+      <c r="N10" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5251,24 +5248,24 @@
         <f>+#REF!*O10</f>
         <v>#REF!</v>
       </c>
-      <c r="AA10" s="97" t="e">
+      <c r="AA10" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB10" s="97" t="e">
+      <c r="AB10" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="94">
+      <c r="A11" s="91">
         <v>10</v>
       </c>
-      <c r="L11" s="94" t="e">
+      <c r="L11" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N11" s="94">
+      <c r="N11" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5279,24 +5276,24 @@
         <f>+#REF!*O11</f>
         <v>#REF!</v>
       </c>
-      <c r="AA11" s="97" t="e">
+      <c r="AA11" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB11" s="97" t="e">
+      <c r="AB11" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="94">
+      <c r="A12" s="91">
         <v>11</v>
       </c>
-      <c r="L12" s="94" t="e">
+      <c r="L12" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N12" s="94">
+      <c r="N12" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5307,24 +5304,24 @@
         <f>+#REF!*O12</f>
         <v>#REF!</v>
       </c>
-      <c r="AA12" s="97" t="e">
+      <c r="AA12" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB12" s="97" t="e">
+      <c r="AB12" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94">
+      <c r="A13" s="91">
         <v>12</v>
       </c>
-      <c r="L13" s="94" t="e">
+      <c r="L13" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N13" s="94">
+      <c r="N13" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5335,24 +5332,24 @@
         <f>+#REF!*O13</f>
         <v>#REF!</v>
       </c>
-      <c r="AA13" s="97" t="e">
+      <c r="AA13" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB13" s="97" t="e">
+      <c r="AB13" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="94">
+      <c r="A14" s="91">
         <v>13</v>
       </c>
-      <c r="L14" s="94" t="e">
+      <c r="L14" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N14" s="94">
+      <c r="N14" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5363,24 +5360,24 @@
         <f>+#REF!*O14</f>
         <v>#REF!</v>
       </c>
-      <c r="AA14" s="97" t="e">
+      <c r="AA14" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB14" s="97" t="e">
+      <c r="AB14" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="94">
+      <c r="A15" s="91">
         <v>14</v>
       </c>
-      <c r="L15" s="94" t="e">
+      <c r="L15" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N15" s="94">
+      <c r="N15" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5391,24 +5388,24 @@
         <f>+#REF!*O15</f>
         <v>#REF!</v>
       </c>
-      <c r="AA15" s="97" t="e">
+      <c r="AA15" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB15" s="97" t="e">
+      <c r="AB15" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="94">
+      <c r="A16" s="91">
         <v>15</v>
       </c>
-      <c r="L16" s="94" t="e">
+      <c r="L16" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N16" s="94">
+      <c r="N16" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5419,24 +5416,24 @@
         <f>+#REF!*O16</f>
         <v>#REF!</v>
       </c>
-      <c r="AA16" s="97" t="e">
+      <c r="AA16" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB16" s="97" t="e">
+      <c r="AB16" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="94">
+      <c r="A17" s="91">
         <v>16</v>
       </c>
-      <c r="L17" s="94" t="e">
+      <c r="L17" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N17" s="94">
+      <c r="N17" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5447,24 +5444,24 @@
         <f>+#REF!*O17</f>
         <v>#REF!</v>
       </c>
-      <c r="AA17" s="97" t="e">
+      <c r="AA17" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB17" s="97" t="e">
+      <c r="AB17" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="94">
+      <c r="A18" s="91">
         <v>17</v>
       </c>
-      <c r="L18" s="94" t="e">
+      <c r="L18" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N18" s="94">
+      <c r="N18" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5475,24 +5472,24 @@
         <f>+#REF!*O18</f>
         <v>#REF!</v>
       </c>
-      <c r="AA18" s="97" t="e">
+      <c r="AA18" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB18" s="97" t="e">
+      <c r="AB18" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="94">
+      <c r="A19" s="91">
         <v>18</v>
       </c>
-      <c r="L19" s="94" t="e">
+      <c r="L19" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N19" s="94">
+      <c r="N19" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5503,24 +5500,24 @@
         <f>+#REF!*O19</f>
         <v>#REF!</v>
       </c>
-      <c r="AA19" s="97" t="e">
+      <c r="AA19" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB19" s="97" t="e">
+      <c r="AB19" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="94">
+      <c r="A20" s="91">
         <v>19</v>
       </c>
-      <c r="L20" s="94" t="e">
+      <c r="L20" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N20" s="94">
+      <c r="N20" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5531,24 +5528,24 @@
         <f>+#REF!*O20</f>
         <v>#REF!</v>
       </c>
-      <c r="AA20" s="97" t="e">
+      <c r="AA20" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB20" s="97" t="e">
+      <c r="AB20" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="94">
+      <c r="A21" s="91">
         <v>20</v>
       </c>
-      <c r="L21" s="94" t="e">
+      <c r="L21" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N21" s="94">
+      <c r="N21" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5559,24 +5556,24 @@
         <f>+#REF!*O21</f>
         <v>#REF!</v>
       </c>
-      <c r="AA21" s="97" t="e">
+      <c r="AA21" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB21" s="97" t="e">
+      <c r="AB21" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="94">
+      <c r="A22" s="91">
         <v>21</v>
       </c>
-      <c r="L22" s="94" t="e">
+      <c r="L22" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N22" s="94">
+      <c r="N22" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5587,24 +5584,24 @@
         <f>+#REF!*O22</f>
         <v>#REF!</v>
       </c>
-      <c r="AA22" s="97" t="e">
+      <c r="AA22" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB22" s="97" t="e">
+      <c r="AB22" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="94">
+      <c r="A23" s="91">
         <v>22</v>
       </c>
-      <c r="L23" s="94" t="e">
+      <c r="L23" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N23" s="94">
+      <c r="N23" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5615,24 +5612,24 @@
         <f>+#REF!*O23</f>
         <v>#REF!</v>
       </c>
-      <c r="AA23" s="97" t="e">
+      <c r="AA23" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB23" s="97" t="e">
+      <c r="AB23" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="94">
+      <c r="A24" s="91">
         <v>23</v>
       </c>
-      <c r="L24" s="94" t="e">
+      <c r="L24" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N24" s="94">
+      <c r="N24" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5643,24 +5640,24 @@
         <f>+#REF!*O24</f>
         <v>#REF!</v>
       </c>
-      <c r="AA24" s="97" t="e">
+      <c r="AA24" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB24" s="97" t="e">
+      <c r="AB24" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="94">
+      <c r="A25" s="91">
         <v>24</v>
       </c>
-      <c r="L25" s="94" t="e">
+      <c r="L25" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N25" s="94">
+      <c r="N25" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5671,24 +5668,24 @@
         <f>+#REF!*O25</f>
         <v>#REF!</v>
       </c>
-      <c r="AA25" s="97" t="e">
+      <c r="AA25" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB25" s="97" t="e">
+      <c r="AB25" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="94">
+      <c r="A26" s="91">
         <v>25</v>
       </c>
-      <c r="L26" s="94" t="e">
+      <c r="L26" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N26" s="94">
+      <c r="N26" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5699,24 +5696,24 @@
         <f>+#REF!*O26</f>
         <v>#REF!</v>
       </c>
-      <c r="AA26" s="97" t="e">
+      <c r="AA26" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB26" s="97" t="e">
+      <c r="AB26" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="94">
+      <c r="A27" s="91">
         <v>26</v>
       </c>
-      <c r="L27" s="94" t="e">
+      <c r="L27" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N27" s="94">
+      <c r="N27" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5727,24 +5724,24 @@
         <f>+#REF!*O27</f>
         <v>#REF!</v>
       </c>
-      <c r="AA27" s="97" t="e">
+      <c r="AA27" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB27" s="97" t="e">
+      <c r="AB27" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="94">
+      <c r="A28" s="91">
         <v>27</v>
       </c>
-      <c r="L28" s="94" t="e">
+      <c r="L28" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N28" s="94">
+      <c r="N28" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5755,24 +5752,24 @@
         <f>+#REF!*O28</f>
         <v>#REF!</v>
       </c>
-      <c r="AA28" s="97" t="e">
+      <c r="AA28" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB28" s="97" t="e">
+      <c r="AB28" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="94">
+      <c r="A29" s="91">
         <v>28</v>
       </c>
-      <c r="L29" s="94" t="e">
+      <c r="L29" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N29" s="94">
+      <c r="N29" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5783,24 +5780,24 @@
         <f>+#REF!*O29</f>
         <v>#REF!</v>
       </c>
-      <c r="AA29" s="97" t="e">
+      <c r="AA29" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB29" s="97" t="e">
+      <c r="AB29" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="94">
+      <c r="A30" s="91">
         <v>29</v>
       </c>
-      <c r="L30" s="94" t="e">
+      <c r="L30" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N30" s="94">
+      <c r="N30" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5811,24 +5808,24 @@
         <f>+#REF!*O30</f>
         <v>#REF!</v>
       </c>
-      <c r="AA30" s="97" t="e">
+      <c r="AA30" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB30" s="97" t="e">
+      <c r="AB30" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="94">
+      <c r="A31" s="91">
         <v>30</v>
       </c>
-      <c r="L31" s="94" t="e">
+      <c r="L31" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N31" s="94">
+      <c r="N31" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5839,24 +5836,24 @@
         <f>+#REF!*O31</f>
         <v>#REF!</v>
       </c>
-      <c r="AA31" s="97" t="e">
+      <c r="AA31" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB31" s="97" t="e">
+      <c r="AB31" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A32" s="94">
+      <c r="A32" s="91">
         <v>31</v>
       </c>
-      <c r="L32" s="94" t="e">
+      <c r="L32" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N32" s="94">
+      <c r="N32" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5867,24 +5864,24 @@
         <f>+#REF!*O32</f>
         <v>#REF!</v>
       </c>
-      <c r="AA32" s="97" t="e">
+      <c r="AA32" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB32" s="97" t="e">
+      <c r="AB32" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A33" s="94">
+      <c r="A33" s="91">
         <v>32</v>
       </c>
-      <c r="L33" s="94" t="e">
+      <c r="L33" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N33" s="94">
+      <c r="N33" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5895,24 +5892,24 @@
         <f>+#REF!*O33</f>
         <v>#REF!</v>
       </c>
-      <c r="AA33" s="97" t="e">
+      <c r="AA33" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB33" s="97" t="e">
+      <c r="AB33" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A34" s="94">
+      <c r="A34" s="91">
         <v>33</v>
       </c>
-      <c r="L34" s="94" t="e">
+      <c r="L34" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N34" s="94">
+      <c r="N34" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5923,24 +5920,24 @@
         <f>+#REF!*O34</f>
         <v>#REF!</v>
       </c>
-      <c r="AA34" s="97" t="e">
+      <c r="AA34" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB34" s="97" t="e">
+      <c r="AB34" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A35" s="94">
+      <c r="A35" s="91">
         <v>34</v>
       </c>
-      <c r="L35" s="94" t="e">
+      <c r="L35" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N35" s="94">
+      <c r="N35" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5951,24 +5948,24 @@
         <f>+#REF!*O35</f>
         <v>#REF!</v>
       </c>
-      <c r="AA35" s="97" t="e">
+      <c r="AA35" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB35" s="97" t="e">
+      <c r="AB35" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A36" s="94">
+      <c r="A36" s="91">
         <v>35</v>
       </c>
-      <c r="L36" s="94" t="e">
+      <c r="L36" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N36" s="94">
+      <c r="N36" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -5979,24 +5976,24 @@
         <f>+#REF!*O36</f>
         <v>#REF!</v>
       </c>
-      <c r="AA36" s="97" t="e">
+      <c r="AA36" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB36" s="97" t="e">
+      <c r="AB36" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A37" s="94">
+      <c r="A37" s="91">
         <v>36</v>
       </c>
-      <c r="L37" s="94" t="e">
+      <c r="L37" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N37" s="94">
+      <c r="N37" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6007,24 +6004,24 @@
         <f>+#REF!*O37</f>
         <v>#REF!</v>
       </c>
-      <c r="AA37" s="97" t="e">
+      <c r="AA37" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB37" s="97" t="e">
+      <c r="AB37" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A38" s="94">
+      <c r="A38" s="91">
         <v>37</v>
       </c>
-      <c r="L38" s="94" t="e">
+      <c r="L38" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N38" s="94">
+      <c r="N38" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6035,24 +6032,24 @@
         <f>+#REF!*O38</f>
         <v>#REF!</v>
       </c>
-      <c r="AA38" s="97" t="e">
+      <c r="AA38" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB38" s="97" t="e">
+      <c r="AB38" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A39" s="94">
+      <c r="A39" s="91">
         <v>38</v>
       </c>
-      <c r="L39" s="94" t="e">
+      <c r="L39" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N39" s="94">
+      <c r="N39" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6063,24 +6060,24 @@
         <f>+#REF!*O39</f>
         <v>#REF!</v>
       </c>
-      <c r="AA39" s="97" t="e">
+      <c r="AA39" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB39" s="97" t="e">
+      <c r="AB39" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A40" s="94">
+      <c r="A40" s="91">
         <v>39</v>
       </c>
-      <c r="L40" s="94" t="e">
+      <c r="L40" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N40" s="94">
+      <c r="N40" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6091,24 +6088,24 @@
         <f>+#REF!*O40</f>
         <v>#REF!</v>
       </c>
-      <c r="AA40" s="97" t="e">
+      <c r="AA40" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB40" s="97" t="e">
+      <c r="AB40" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A41" s="94">
+      <c r="A41" s="91">
         <v>40</v>
       </c>
-      <c r="L41" s="94" t="e">
+      <c r="L41" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N41" s="94">
+      <c r="N41" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6119,24 +6116,24 @@
         <f>+#REF!*O41</f>
         <v>#REF!</v>
       </c>
-      <c r="AA41" s="97" t="e">
+      <c r="AA41" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB41" s="97" t="e">
+      <c r="AB41" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A42" s="94">
+      <c r="A42" s="91">
         <v>41</v>
       </c>
-      <c r="L42" s="94" t="e">
+      <c r="L42" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N42" s="94">
+      <c r="N42" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6147,24 +6144,24 @@
         <f>+#REF!*O42</f>
         <v>#REF!</v>
       </c>
-      <c r="AA42" s="97" t="e">
+      <c r="AA42" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB42" s="97" t="e">
+      <c r="AB42" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A43" s="94">
+      <c r="A43" s="91">
         <v>42</v>
       </c>
-      <c r="L43" s="94" t="e">
+      <c r="L43" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N43" s="94">
+      <c r="N43" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6175,24 +6172,24 @@
         <f>+#REF!*O43</f>
         <v>#REF!</v>
       </c>
-      <c r="AA43" s="97" t="e">
+      <c r="AA43" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB43" s="97" t="e">
+      <c r="AB43" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A44" s="94">
+      <c r="A44" s="91">
         <v>43</v>
       </c>
-      <c r="L44" s="94" t="e">
+      <c r="L44" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N44" s="94">
+      <c r="N44" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6203,24 +6200,24 @@
         <f>+#REF!*O44</f>
         <v>#REF!</v>
       </c>
-      <c r="AA44" s="97" t="e">
+      <c r="AA44" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB44" s="97" t="e">
+      <c r="AB44" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A45" s="94">
+      <c r="A45" s="91">
         <v>44</v>
       </c>
-      <c r="L45" s="94" t="e">
+      <c r="L45" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N45" s="94">
+      <c r="N45" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6231,24 +6228,24 @@
         <f>+#REF!*O45</f>
         <v>#REF!</v>
       </c>
-      <c r="AA45" s="97" t="e">
+      <c r="AA45" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB45" s="97" t="e">
+      <c r="AB45" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A46" s="94">
+      <c r="A46" s="91">
         <v>45</v>
       </c>
-      <c r="L46" s="94" t="e">
+      <c r="L46" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N46" s="94">
+      <c r="N46" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6259,24 +6256,24 @@
         <f>+#REF!*O46</f>
         <v>#REF!</v>
       </c>
-      <c r="AA46" s="97" t="e">
+      <c r="AA46" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB46" s="97" t="e">
+      <c r="AB46" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A47" s="94">
+      <c r="A47" s="91">
         <v>46</v>
       </c>
-      <c r="L47" s="94" t="e">
+      <c r="L47" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N47" s="94">
+      <c r="N47" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6287,24 +6284,24 @@
         <f>+#REF!*O47</f>
         <v>#REF!</v>
       </c>
-      <c r="AA47" s="97" t="e">
+      <c r="AA47" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB47" s="97" t="e">
+      <c r="AB47" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A48" s="94">
+      <c r="A48" s="91">
         <v>47</v>
       </c>
-      <c r="L48" s="94" t="e">
+      <c r="L48" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N48" s="94">
+      <c r="N48" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6315,24 +6312,24 @@
         <f>+#REF!*O48</f>
         <v>#REF!</v>
       </c>
-      <c r="AA48" s="97" t="e">
+      <c r="AA48" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB48" s="97" t="e">
+      <c r="AB48" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="49" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="94">
+      <c r="A49" s="91">
         <v>48</v>
       </c>
-      <c r="L49" s="94" t="e">
+      <c r="L49" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N49" s="94">
+      <c r="N49" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6343,24 +6340,24 @@
         <f>+#REF!*O49</f>
         <v>#REF!</v>
       </c>
-      <c r="AA49" s="97" t="e">
+      <c r="AA49" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB49" s="97" t="e">
+      <c r="AB49" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A50" s="94">
+      <c r="A50" s="91">
         <v>49</v>
       </c>
-      <c r="L50" s="94" t="e">
+      <c r="L50" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N50" s="94">
+      <c r="N50" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6371,24 +6368,24 @@
         <f>+#REF!*O50</f>
         <v>#REF!</v>
       </c>
-      <c r="AA50" s="97" t="e">
+      <c r="AA50" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB50" s="97" t="e">
+      <c r="AB50" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A51" s="94">
+      <c r="A51" s="91">
         <v>50</v>
       </c>
-      <c r="L51" s="94" t="e">
+      <c r="L51" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N51" s="94">
+      <c r="N51" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6399,24 +6396,24 @@
         <f>+#REF!*O51</f>
         <v>#REF!</v>
       </c>
-      <c r="AA51" s="97" t="e">
+      <c r="AA51" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB51" s="97" t="e">
+      <c r="AB51" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A52" s="94">
+      <c r="A52" s="91">
         <v>51</v>
       </c>
-      <c r="L52" s="94" t="e">
+      <c r="L52" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N52" s="94">
+      <c r="N52" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6427,24 +6424,24 @@
         <f>+#REF!*O52</f>
         <v>#REF!</v>
       </c>
-      <c r="AA52" s="97" t="e">
+      <c r="AA52" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB52" s="97" t="e">
+      <c r="AB52" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A53" s="94">
+      <c r="A53" s="91">
         <v>52</v>
       </c>
-      <c r="L53" s="94" t="e">
+      <c r="L53" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N53" s="94">
+      <c r="N53" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6455,24 +6452,24 @@
         <f>+#REF!*O53</f>
         <v>#REF!</v>
       </c>
-      <c r="AA53" s="97" t="e">
+      <c r="AA53" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB53" s="97" t="e">
+      <c r="AB53" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A54" s="94">
+      <c r="A54" s="91">
         <v>53</v>
       </c>
-      <c r="L54" s="94" t="e">
+      <c r="L54" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N54" s="94">
+      <c r="N54" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6483,24 +6480,24 @@
         <f>+#REF!*O54</f>
         <v>#REF!</v>
       </c>
-      <c r="AA54" s="97" t="e">
+      <c r="AA54" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB54" s="97" t="e">
+      <c r="AB54" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A55" s="94">
+      <c r="A55" s="91">
         <v>54</v>
       </c>
-      <c r="L55" s="94" t="e">
+      <c r="L55" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N55" s="94">
+      <c r="N55" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6511,24 +6508,24 @@
         <f>+#REF!*O55</f>
         <v>#REF!</v>
       </c>
-      <c r="AA55" s="97" t="e">
+      <c r="AA55" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB55" s="97" t="e">
+      <c r="AB55" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A56" s="94">
+      <c r="A56" s="91">
         <v>55</v>
       </c>
-      <c r="L56" s="94" t="e">
+      <c r="L56" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N56" s="94">
+      <c r="N56" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6539,24 +6536,24 @@
         <f>+#REF!*O56</f>
         <v>#REF!</v>
       </c>
-      <c r="AA56" s="97" t="e">
+      <c r="AA56" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB56" s="97" t="e">
+      <c r="AB56" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A57" s="94">
+      <c r="A57" s="91">
         <v>56</v>
       </c>
-      <c r="L57" s="94" t="e">
+      <c r="L57" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N57" s="94">
+      <c r="N57" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6567,24 +6564,24 @@
         <f>+#REF!*O57</f>
         <v>#REF!</v>
       </c>
-      <c r="AA57" s="97" t="e">
+      <c r="AA57" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB57" s="97" t="e">
+      <c r="AB57" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A58" s="94">
+      <c r="A58" s="91">
         <v>57</v>
       </c>
-      <c r="L58" s="94" t="e">
+      <c r="L58" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N58" s="94">
+      <c r="N58" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6595,24 +6592,24 @@
         <f>+#REF!*O58</f>
         <v>#REF!</v>
       </c>
-      <c r="AA58" s="97" t="e">
+      <c r="AA58" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB58" s="97" t="e">
+      <c r="AB58" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A59" s="94">
+      <c r="A59" s="91">
         <v>58</v>
       </c>
-      <c r="L59" s="94" t="e">
+      <c r="L59" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N59" s="94">
+      <c r="N59" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6623,24 +6620,24 @@
         <f>+#REF!*O59</f>
         <v>#REF!</v>
       </c>
-      <c r="AA59" s="97" t="e">
+      <c r="AA59" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB59" s="97" t="e">
+      <c r="AB59" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A60" s="94">
+      <c r="A60" s="91">
         <v>59</v>
       </c>
-      <c r="L60" s="94" t="e">
+      <c r="L60" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N60" s="94">
+      <c r="N60" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6651,24 +6648,24 @@
         <f>+#REF!*O60</f>
         <v>#REF!</v>
       </c>
-      <c r="AA60" s="97" t="e">
+      <c r="AA60" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB60" s="97" t="e">
+      <c r="AB60" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="61" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="94">
+      <c r="A61" s="91">
         <v>60</v>
       </c>
-      <c r="L61" s="94" t="e">
+      <c r="L61" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N61" s="94">
+      <c r="N61" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6679,24 +6676,24 @@
         <f>+#REF!*O61</f>
         <v>#REF!</v>
       </c>
-      <c r="AA61" s="97" t="e">
+      <c r="AA61" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB61" s="97" t="e">
+      <c r="AB61" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="62" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A62" s="94">
+      <c r="A62" s="91">
         <v>61</v>
       </c>
-      <c r="L62" s="94" t="e">
+      <c r="L62" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N62" s="94">
+      <c r="N62" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6707,24 +6704,24 @@
         <f>+#REF!*O62</f>
         <v>#REF!</v>
       </c>
-      <c r="AA62" s="97" t="e">
+      <c r="AA62" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB62" s="97" t="e">
+      <c r="AB62" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="63" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A63" s="94">
+      <c r="A63" s="91">
         <v>62</v>
       </c>
-      <c r="L63" s="94" t="e">
+      <c r="L63" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N63" s="94">
+      <c r="N63" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6735,24 +6732,24 @@
         <f>+#REF!*O63</f>
         <v>#REF!</v>
       </c>
-      <c r="AA63" s="97" t="e">
+      <c r="AA63" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB63" s="97" t="e">
+      <c r="AB63" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A64" s="94">
+      <c r="A64" s="91">
         <v>63</v>
       </c>
-      <c r="L64" s="94" t="e">
+      <c r="L64" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N64" s="94">
+      <c r="N64" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6763,24 +6760,24 @@
         <f>+#REF!*O64</f>
         <v>#REF!</v>
       </c>
-      <c r="AA64" s="97" t="e">
+      <c r="AA64" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB64" s="97" t="e">
+      <c r="AB64" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A65" s="94">
+      <c r="A65" s="91">
         <v>64</v>
       </c>
-      <c r="L65" s="94" t="e">
+      <c r="L65" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N65" s="94">
+      <c r="N65" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6791,24 +6788,24 @@
         <f>+#REF!*O65</f>
         <v>#REF!</v>
       </c>
-      <c r="AA65" s="97" t="e">
+      <c r="AA65" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB65" s="97" t="e">
+      <c r="AB65" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A66" s="94">
+      <c r="A66" s="91">
         <v>65</v>
       </c>
-      <c r="L66" s="94" t="e">
+      <c r="L66" s="91" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N66" s="94">
+      <c r="N66" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6819,24 +6816,24 @@
         <f>+#REF!*O66</f>
         <v>#REF!</v>
       </c>
-      <c r="AA66" s="97" t="e">
+      <c r="AA66" s="94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB66" s="97" t="e">
+      <c r="AB66" s="94" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A67" s="94">
+      <c r="A67" s="91">
         <v>66</v>
       </c>
-      <c r="L67" s="94" t="e">
+      <c r="L67" s="91" t="e">
         <f t="shared" ref="L67:L97" si="4">I67/J67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N67" s="94">
+      <c r="N67" s="91">
         <f t="shared" ref="N67:N97" si="5">5-O67</f>
         <v>0</v>
       </c>
@@ -6847,24 +6844,24 @@
         <f>+#REF!*O67</f>
         <v>#REF!</v>
       </c>
-      <c r="AA67" s="97" t="e">
+      <c r="AA67" s="94" t="e">
         <f t="shared" ref="AA67:AA97" si="6">+MAX($Y$2:$Y$97)/Y67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB67" s="97" t="e">
+      <c r="AB67" s="94" t="e">
         <f t="shared" ref="AB67:AB97" si="7">AA67</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A68" s="94">
+      <c r="A68" s="91">
         <v>67</v>
       </c>
-      <c r="L68" s="94" t="e">
+      <c r="L68" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N68" s="94">
+      <c r="N68" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6875,24 +6872,24 @@
         <f>+#REF!*O68</f>
         <v>#REF!</v>
       </c>
-      <c r="AA68" s="97" t="e">
+      <c r="AA68" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB68" s="97" t="e">
+      <c r="AB68" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A69" s="94">
+      <c r="A69" s="91">
         <v>68</v>
       </c>
-      <c r="L69" s="94" t="e">
+      <c r="L69" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N69" s="94">
+      <c r="N69" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6903,24 +6900,24 @@
         <f>+#REF!*O69</f>
         <v>#REF!</v>
       </c>
-      <c r="AA69" s="97" t="e">
+      <c r="AA69" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB69" s="97" t="e">
+      <c r="AB69" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="70" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A70" s="94">
+      <c r="A70" s="91">
         <v>69</v>
       </c>
-      <c r="L70" s="94" t="e">
+      <c r="L70" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N70" s="94">
+      <c r="N70" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6931,24 +6928,24 @@
         <f>+#REF!*O70</f>
         <v>#REF!</v>
       </c>
-      <c r="AA70" s="97" t="e">
+      <c r="AA70" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB70" s="97" t="e">
+      <c r="AB70" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A71" s="94">
+      <c r="A71" s="91">
         <v>70</v>
       </c>
-      <c r="L71" s="94" t="e">
+      <c r="L71" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N71" s="94">
+      <c r="N71" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6959,24 +6956,24 @@
         <f>+#REF!*O71</f>
         <v>#REF!</v>
       </c>
-      <c r="AA71" s="97" t="e">
+      <c r="AA71" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB71" s="97" t="e">
+      <c r="AB71" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A72" s="94">
+      <c r="A72" s="91">
         <v>71</v>
       </c>
-      <c r="L72" s="94" t="e">
+      <c r="L72" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N72" s="94">
+      <c r="N72" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6987,24 +6984,24 @@
         <f>+#REF!*O72</f>
         <v>#REF!</v>
       </c>
-      <c r="AA72" s="97" t="e">
+      <c r="AA72" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB72" s="97" t="e">
+      <c r="AB72" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A73" s="94">
+      <c r="A73" s="91">
         <v>72</v>
       </c>
-      <c r="L73" s="94" t="e">
+      <c r="L73" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N73" s="94">
+      <c r="N73" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7015,24 +7012,24 @@
         <f>+#REF!*O73</f>
         <v>#REF!</v>
       </c>
-      <c r="AA73" s="97" t="e">
+      <c r="AA73" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB73" s="97" t="e">
+      <c r="AB73" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A74" s="94">
+      <c r="A74" s="91">
         <v>73</v>
       </c>
-      <c r="L74" s="94" t="e">
+      <c r="L74" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N74" s="94">
+      <c r="N74" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7043,24 +7040,24 @@
         <f>+#REF!*O74</f>
         <v>#REF!</v>
       </c>
-      <c r="AA74" s="97" t="e">
+      <c r="AA74" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB74" s="97" t="e">
+      <c r="AB74" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A75" s="94">
+      <c r="A75" s="91">
         <v>74</v>
       </c>
-      <c r="L75" s="94" t="e">
+      <c r="L75" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N75" s="94">
+      <c r="N75" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7071,24 +7068,24 @@
         <f>+#REF!*O75</f>
         <v>#REF!</v>
       </c>
-      <c r="AA75" s="97" t="e">
+      <c r="AA75" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB75" s="97" t="e">
+      <c r="AB75" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A76" s="94">
+      <c r="A76" s="91">
         <v>75</v>
       </c>
-      <c r="L76" s="94" t="e">
+      <c r="L76" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N76" s="94">
+      <c r="N76" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7099,24 +7096,24 @@
         <f>+#REF!*O76</f>
         <v>#REF!</v>
       </c>
-      <c r="AA76" s="97" t="e">
+      <c r="AA76" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB76" s="97" t="e">
+      <c r="AB76" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A77" s="94">
+      <c r="A77" s="91">
         <v>76</v>
       </c>
-      <c r="L77" s="94" t="e">
+      <c r="L77" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N77" s="94">
+      <c r="N77" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7127,24 +7124,24 @@
         <f>+#REF!*O77</f>
         <v>#REF!</v>
       </c>
-      <c r="AA77" s="97" t="e">
+      <c r="AA77" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB77" s="97" t="e">
+      <c r="AB77" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="78" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A78" s="94">
+      <c r="A78" s="91">
         <v>77</v>
       </c>
-      <c r="L78" s="94" t="e">
+      <c r="L78" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N78" s="94">
+      <c r="N78" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7155,24 +7152,24 @@
         <f>+#REF!*O78</f>
         <v>#REF!</v>
       </c>
-      <c r="AA78" s="97" t="e">
+      <c r="AA78" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB78" s="97" t="e">
+      <c r="AB78" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A79" s="94">
+      <c r="A79" s="91">
         <v>78</v>
       </c>
-      <c r="L79" s="94" t="e">
+      <c r="L79" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N79" s="94">
+      <c r="N79" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7183,24 +7180,24 @@
         <f>+#REF!*O79</f>
         <v>#REF!</v>
       </c>
-      <c r="AA79" s="97" t="e">
+      <c r="AA79" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB79" s="97" t="e">
+      <c r="AB79" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A80" s="94">
+      <c r="A80" s="91">
         <v>79</v>
       </c>
-      <c r="L80" s="94" t="e">
+      <c r="L80" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N80" s="94">
+      <c r="N80" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7211,24 +7208,24 @@
         <f>+#REF!*O80</f>
         <v>#REF!</v>
       </c>
-      <c r="AA80" s="97" t="e">
+      <c r="AA80" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB80" s="97" t="e">
+      <c r="AB80" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A81" s="94">
+      <c r="A81" s="91">
         <v>80</v>
       </c>
-      <c r="L81" s="94" t="e">
+      <c r="L81" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N81" s="94">
+      <c r="N81" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7239,24 +7236,24 @@
         <f>+#REF!*O81</f>
         <v>#REF!</v>
       </c>
-      <c r="AA81" s="97" t="e">
+      <c r="AA81" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB81" s="97" t="e">
+      <c r="AB81" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A82" s="94">
+      <c r="A82" s="91">
         <v>81</v>
       </c>
-      <c r="L82" s="94" t="e">
+      <c r="L82" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N82" s="94">
+      <c r="N82" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7267,24 +7264,24 @@
         <f>+#REF!*O82</f>
         <v>#REF!</v>
       </c>
-      <c r="AA82" s="97" t="e">
+      <c r="AA82" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB82" s="97" t="e">
+      <c r="AB82" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A83" s="94">
+      <c r="A83" s="91">
         <v>82</v>
       </c>
-      <c r="L83" s="94" t="e">
+      <c r="L83" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N83" s="94">
+      <c r="N83" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7295,24 +7292,24 @@
         <f>+#REF!*O83</f>
         <v>#REF!</v>
       </c>
-      <c r="AA83" s="97" t="e">
+      <c r="AA83" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB83" s="97" t="e">
+      <c r="AB83" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A84" s="94">
+      <c r="A84" s="91">
         <v>83</v>
       </c>
-      <c r="L84" s="94" t="e">
+      <c r="L84" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N84" s="94">
+      <c r="N84" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7323,24 +7320,24 @@
         <f>+#REF!*O84</f>
         <v>#REF!</v>
       </c>
-      <c r="AA84" s="97" t="e">
+      <c r="AA84" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB84" s="97" t="e">
+      <c r="AB84" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="94">
+      <c r="A85" s="91">
         <v>84</v>
       </c>
-      <c r="L85" s="94" t="e">
+      <c r="L85" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N85" s="94">
+      <c r="N85" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7351,24 +7348,24 @@
         <f>+#REF!*O85</f>
         <v>#REF!</v>
       </c>
-      <c r="AA85" s="97" t="e">
+      <c r="AA85" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB85" s="97" t="e">
+      <c r="AB85" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A86" s="94">
+      <c r="A86" s="91">
         <v>85</v>
       </c>
-      <c r="L86" s="94" t="e">
+      <c r="L86" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N86" s="94">
+      <c r="N86" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7379,24 +7376,24 @@
         <f>+#REF!*O86</f>
         <v>#REF!</v>
       </c>
-      <c r="AA86" s="97" t="e">
+      <c r="AA86" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB86" s="97" t="e">
+      <c r="AB86" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A87" s="94">
+      <c r="A87" s="91">
         <v>86</v>
       </c>
-      <c r="L87" s="94" t="e">
+      <c r="L87" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N87" s="94">
+      <c r="N87" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7407,24 +7404,24 @@
         <f>+#REF!*O87</f>
         <v>#REF!</v>
       </c>
-      <c r="AA87" s="97" t="e">
+      <c r="AA87" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB87" s="97" t="e">
+      <c r="AB87" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A88" s="94">
+      <c r="A88" s="91">
         <v>87</v>
       </c>
-      <c r="L88" s="94" t="e">
+      <c r="L88" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N88" s="94">
+      <c r="N88" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7435,24 +7432,24 @@
         <f>+#REF!*O88</f>
         <v>#REF!</v>
       </c>
-      <c r="AA88" s="97" t="e">
+      <c r="AA88" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB88" s="97" t="e">
+      <c r="AB88" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A89" s="94">
+      <c r="A89" s="91">
         <v>88</v>
       </c>
-      <c r="L89" s="94" t="e">
+      <c r="L89" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N89" s="94">
+      <c r="N89" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7463,24 +7460,24 @@
         <f>+#REF!*O89</f>
         <v>#REF!</v>
       </c>
-      <c r="AA89" s="97" t="e">
+      <c r="AA89" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB89" s="97" t="e">
+      <c r="AB89" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="90" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A90" s="94">
+      <c r="A90" s="91">
         <v>89</v>
       </c>
-      <c r="L90" s="94" t="e">
+      <c r="L90" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N90" s="94">
+      <c r="N90" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7491,24 +7488,24 @@
         <f>+#REF!*O90</f>
         <v>#REF!</v>
       </c>
-      <c r="AA90" s="97" t="e">
+      <c r="AA90" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB90" s="97" t="e">
+      <c r="AB90" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="91" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A91" s="94">
+      <c r="A91" s="91">
         <v>90</v>
       </c>
-      <c r="L91" s="94" t="e">
+      <c r="L91" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N91" s="94">
+      <c r="N91" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7519,24 +7516,24 @@
         <f>+#REF!*O91</f>
         <v>#REF!</v>
       </c>
-      <c r="AA91" s="97" t="e">
+      <c r="AA91" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB91" s="97" t="e">
+      <c r="AB91" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A92" s="94">
+      <c r="A92" s="91">
         <v>91</v>
       </c>
-      <c r="L92" s="94" t="e">
+      <c r="L92" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N92" s="94">
+      <c r="N92" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7547,24 +7544,24 @@
         <f>+#REF!*O92</f>
         <v>#REF!</v>
       </c>
-      <c r="AA92" s="97" t="e">
+      <c r="AA92" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB92" s="97" t="e">
+      <c r="AB92" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A93" s="94">
+      <c r="A93" s="91">
         <v>92</v>
       </c>
-      <c r="L93" s="94" t="e">
+      <c r="L93" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N93" s="94">
+      <c r="N93" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7575,24 +7572,24 @@
         <f>+#REF!*O93</f>
         <v>#REF!</v>
       </c>
-      <c r="AA93" s="97" t="e">
+      <c r="AA93" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB93" s="97" t="e">
+      <c r="AB93" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="94" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A94" s="94">
+      <c r="A94" s="91">
         <v>93</v>
       </c>
-      <c r="L94" s="94" t="e">
+      <c r="L94" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N94" s="94">
+      <c r="N94" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7603,24 +7600,24 @@
         <f>+#REF!*O94</f>
         <v>#REF!</v>
       </c>
-      <c r="AA94" s="97" t="e">
+      <c r="AA94" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB94" s="97" t="e">
+      <c r="AB94" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="95" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A95" s="94">
+      <c r="A95" s="91">
         <v>94</v>
       </c>
-      <c r="L95" s="94" t="e">
+      <c r="L95" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N95" s="94">
+      <c r="N95" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7631,24 +7628,24 @@
         <f>+#REF!*O95</f>
         <v>#REF!</v>
       </c>
-      <c r="AA95" s="97" t="e">
+      <c r="AA95" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB95" s="97" t="e">
+      <c r="AB95" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A96" s="94">
+      <c r="A96" s="91">
         <v>95</v>
       </c>
-      <c r="L96" s="94" t="e">
+      <c r="L96" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N96" s="94">
+      <c r="N96" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7659,24 +7656,24 @@
         <f>+#REF!*O96</f>
         <v>#REF!</v>
       </c>
-      <c r="AA96" s="97" t="e">
+      <c r="AA96" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB96" s="97" t="e">
+      <c r="AB96" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A97" s="94">
+      <c r="A97" s="91">
         <v>96</v>
       </c>
-      <c r="L97" s="94" t="e">
+      <c r="L97" s="91" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N97" s="94">
+      <c r="N97" s="91">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -7687,17 +7684,17 @@
         <f>+#REF!*O97</f>
         <v>#REF!</v>
       </c>
-      <c r="AA97" s="97" t="e">
+      <c r="AA97" s="94" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB97" s="97" t="e">
+      <c r="AB97" s="94" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="AB98" s="97"/>
+      <c r="AB98" s="94"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="O2:O97">
@@ -7777,179 +7774,179 @@
   <sheetData>
     <row r="1" spans="1:37" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="15"/>
-      <c r="C1" s="177" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
+      <c r="C1" s="104" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="Q1" s="15"/>
     </row>
     <row r="2" spans="1:37" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="179"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2"/>
-      <c r="O2" s="170" t="s">
+      <c r="O2" s="128" t="s">
         <v>107</v>
       </c>
-      <c r="P2" s="170"/>
-      <c r="Q2" s="170"/>
-      <c r="R2" s="170"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
+      <c r="R2" s="128"/>
     </row>
     <row r="3" spans="1:37" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="180" t="s">
+      <c r="A3" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="181"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3"/>
       <c r="N3"/>
-      <c r="O3" s="170"/>
-      <c r="P3" s="170"/>
-      <c r="Q3" s="170"/>
-      <c r="R3" s="170"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
     </row>
     <row r="4" spans="1:37" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="97" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="172"/>
-      <c r="C4" s="172"/>
-      <c r="D4" s="172"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="172"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="156"/>
-      <c r="I4" s="156"/>
-      <c r="O4" s="170"/>
-      <c r="P4" s="170"/>
-      <c r="Q4" s="170"/>
-      <c r="R4" s="170"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="128"/>
+      <c r="Q4" s="128"/>
+      <c r="R4" s="128"/>
     </row>
     <row r="5" spans="1:37" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="171" t="s">
+      <c r="A5" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="172"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156"/>
-      <c r="I5" s="156"/>
-      <c r="O5" s="170"/>
-      <c r="P5" s="170"/>
-      <c r="Q5" s="170"/>
-      <c r="R5" s="170"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="O5" s="128"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="128"/>
       <c r="AK5" s="18"/>
     </row>
     <row r="6" spans="1:37" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="171" t="s">
+      <c r="A6" s="97" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="172"/>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
       <c r="K6" s="16" t="s">
         <v>45</v>
       </c>
       <c r="L6" s="17"/>
-      <c r="O6" s="170"/>
-      <c r="P6" s="170"/>
-      <c r="Q6" s="170"/>
-      <c r="R6" s="170"/>
+      <c r="O6" s="128"/>
+      <c r="P6" s="128"/>
+      <c r="Q6" s="128"/>
+      <c r="R6" s="128"/>
       <c r="AK6" s="18"/>
     </row>
     <row r="7" spans="1:37" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="171" t="s">
+      <c r="A7" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="172"/>
-      <c r="C7" s="172"/>
-      <c r="D7" s="172"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="173" t="s">
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="174"/>
+      <c r="K7" s="101"/>
       <c r="L7" s="17"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="170"/>
-      <c r="Q7" s="170"/>
-      <c r="R7" s="170"/>
+      <c r="O7" s="128"/>
+      <c r="P7" s="128"/>
+      <c r="Q7" s="128"/>
+      <c r="R7" s="128"/>
       <c r="AK7" s="18"/>
     </row>
     <row r="8" spans="1:37" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="171" t="s">
+      <c r="A8" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="172"/>
-      <c r="C8" s="172"/>
-      <c r="D8" s="172"/>
-      <c r="E8" s="172"/>
-      <c r="F8" s="172"/>
-      <c r="G8" s="156"/>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
       <c r="K8" s="57"/>
       <c r="L8" s="58" t="s">
         <v>113</v>
       </c>
       <c r="M8" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="O8" s="170"/>
-      <c r="P8" s="170"/>
-      <c r="Q8" s="170"/>
-      <c r="R8" s="170"/>
+        <v>158</v>
+      </c>
+      <c r="O8" s="128"/>
+      <c r="P8" s="128"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
       <c r="AK8" s="18"/>
     </row>
     <row r="9" spans="1:37" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="153" t="s">
+      <c r="A9" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="154"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="155"/>
-      <c r="H9" s="155"/>
-      <c r="I9" s="155"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
       <c r="K9" s="60"/>
       <c r="L9" s="61" t="s">
         <v>115</v>
@@ -7957,23 +7954,23 @@
       <c r="M9" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="O9" s="170"/>
-      <c r="P9" s="170"/>
-      <c r="Q9" s="170"/>
-      <c r="R9" s="170"/>
+      <c r="O9" s="128"/>
+      <c r="P9" s="128"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="128"/>
     </row>
     <row r="10" spans="1:37" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="153" t="s">
+      <c r="A10" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="154"/>
-      <c r="C10" s="154"/>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
       <c r="K10" s="60"/>
       <c r="L10" s="58" t="s">
         <v>116</v>
@@ -7981,23 +7978,23 @@
       <c r="M10" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="O10" s="170"/>
-      <c r="P10" s="170"/>
-      <c r="Q10" s="170"/>
-      <c r="R10" s="170"/>
+      <c r="O10" s="128"/>
+      <c r="P10" s="128"/>
+      <c r="Q10" s="128"/>
+      <c r="R10" s="128"/>
     </row>
     <row r="11" spans="1:37" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="157" t="s">
+      <c r="A11" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="159"/>
-      <c r="H11" s="159"/>
-      <c r="I11" s="159"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
       <c r="K11" s="60"/>
       <c r="L11" s="63" t="s">
         <v>117</v>
@@ -8007,12 +8004,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="153" t="s">
+      <c r="A12" s="112" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="160"/>
-      <c r="C12" s="160"/>
-      <c r="D12" s="161"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="119"/>
       <c r="E12" s="65"/>
       <c r="F12" s="19" t="b">
         <f>MOD(E12,8)=0</f>
@@ -8029,12 +8026,12 @@
       <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:37" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="153" t="s">
+      <c r="A13" s="112" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="160"/>
-      <c r="C13" s="160"/>
-      <c r="D13" s="161"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="119"/>
       <c r="E13" s="66"/>
       <c r="F13" s="19" t="b">
         <f>MOD(E13,12)=0</f>
@@ -8051,22 +8048,22 @@
       <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:37" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="162" t="s">
+      <c r="B14" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="163"/>
-      <c r="D14" s="163"/>
-      <c r="E14" s="163"/>
-      <c r="F14" s="163"/>
-      <c r="G14" s="163"/>
-      <c r="H14" s="163"/>
-      <c r="I14" s="163"/>
-      <c r="J14" s="163"/>
-      <c r="K14" s="163"/>
-      <c r="L14" s="163"/>
-      <c r="M14" s="163"/>
-      <c r="N14" s="163"/>
-      <c r="O14" s="164"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="121"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="122"/>
     </row>
     <row r="15" spans="1:37" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21"/>
@@ -8614,51 +8611,51 @@
       <c r="B26" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="98">
+      <c r="C26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$2,prep_table!$O$2)</f>
         <v>5</v>
       </c>
-      <c r="D26" s="98">
+      <c r="D26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$3,prep_table!$O$10)</f>
         <v>5</v>
       </c>
-      <c r="E26" s="98">
+      <c r="E26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$4,prep_table!$O$18)</f>
         <v>5</v>
       </c>
-      <c r="F26" s="98">
+      <c r="F26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$5,prep_table!$O$26)</f>
         <v>5</v>
       </c>
-      <c r="G26" s="98">
+      <c r="G26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$6,prep_table!$O$34)</f>
         <v>5</v>
       </c>
-      <c r="H26" s="98">
+      <c r="H26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$7,prep_table!$O$42)</f>
         <v>5</v>
       </c>
-      <c r="I26" s="98">
+      <c r="I26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$8,prep_table!$O$50)</f>
         <v>5</v>
       </c>
-      <c r="J26" s="98">
+      <c r="J26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$9,prep_table!$O$58)</f>
         <v>5</v>
       </c>
-      <c r="K26" s="98">
+      <c r="K26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$10,prep_table!$O$66)</f>
         <v>5</v>
       </c>
-      <c r="L26" s="98">
+      <c r="L26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$11,prep_table!$O$74)</f>
         <v>5</v>
       </c>
-      <c r="M26" s="98">
+      <c r="M26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$12,prep_table!$O$82)</f>
         <v>5</v>
       </c>
-      <c r="N26" s="98">
+      <c r="N26" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$13,prep_table!$O$90)</f>
         <v>5</v>
       </c>
@@ -8681,51 +8678,51 @@
       <c r="B27" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="98">
+      <c r="C27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$14,prep_table!$O$3)</f>
         <v>5</v>
       </c>
-      <c r="D27" s="98">
+      <c r="D27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$15,prep_table!$O$11)</f>
         <v>5</v>
       </c>
-      <c r="E27" s="98">
+      <c r="E27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$16,prep_table!$O$19)</f>
         <v>5</v>
       </c>
-      <c r="F27" s="98">
+      <c r="F27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$17,prep_table!$O$27)</f>
         <v>5</v>
       </c>
-      <c r="G27" s="98">
+      <c r="G27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$18,prep_table!$O$35)</f>
         <v>5</v>
       </c>
-      <c r="H27" s="98">
+      <c r="H27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$19,prep_table!$O$43)</f>
         <v>5</v>
       </c>
-      <c r="I27" s="98">
+      <c r="I27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$20,prep_table!$O$51)</f>
         <v>5</v>
       </c>
-      <c r="J27" s="98">
+      <c r="J27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$21,prep_table!$O$59)</f>
         <v>5</v>
       </c>
-      <c r="K27" s="98">
+      <c r="K27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$22,prep_table!$O$67)</f>
         <v>5</v>
       </c>
-      <c r="L27" s="98">
+      <c r="L27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$23,prep_table!$O$75)</f>
         <v>5</v>
       </c>
-      <c r="M27" s="98">
+      <c r="M27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$24,prep_table!$O$83)</f>
         <v>5</v>
       </c>
-      <c r="N27" s="98">
+      <c r="N27" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$25,prep_table!$O$91)</f>
         <v>5</v>
       </c>
@@ -8748,51 +8745,51 @@
       <c r="B28" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="98">
+      <c r="C28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$26,prep_table!$O$4)</f>
         <v>5</v>
       </c>
-      <c r="D28" s="98">
+      <c r="D28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$27,prep_table!$O$12)</f>
         <v>5</v>
       </c>
-      <c r="E28" s="98">
+      <c r="E28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$28,prep_table!$O$20)</f>
         <v>5</v>
       </c>
-      <c r="F28" s="98">
+      <c r="F28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$29,prep_table!$O$28)</f>
         <v>5</v>
       </c>
-      <c r="G28" s="98">
+      <c r="G28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$30,prep_table!$O$36)</f>
         <v>5</v>
       </c>
-      <c r="H28" s="98">
+      <c r="H28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$31,prep_table!$O$44)</f>
         <v>5</v>
       </c>
-      <c r="I28" s="98">
+      <c r="I28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$32,prep_table!$O$52)</f>
         <v>5</v>
       </c>
-      <c r="J28" s="98">
+      <c r="J28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$33,prep_table!$O$60)</f>
         <v>5</v>
       </c>
-      <c r="K28" s="98">
+      <c r="K28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$34,prep_table!$O$68)</f>
         <v>5</v>
       </c>
-      <c r="L28" s="98">
+      <c r="L28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$35,prep_table!$O$76)</f>
         <v>5</v>
       </c>
-      <c r="M28" s="98">
+      <c r="M28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$36,prep_table!$O$84)</f>
         <v>5</v>
       </c>
-      <c r="N28" s="98">
+      <c r="N28" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$37,prep_table!$O$92)</f>
         <v>5</v>
       </c>
@@ -8815,51 +8812,51 @@
       <c r="B29" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="98">
+      <c r="C29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$38,prep_table!$O$5)</f>
         <v>5</v>
       </c>
-      <c r="D29" s="98">
+      <c r="D29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$39,prep_table!$O$13)</f>
         <v>5</v>
       </c>
-      <c r="E29" s="98">
+      <c r="E29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$40,prep_table!$O$21)</f>
         <v>5</v>
       </c>
-      <c r="F29" s="98">
+      <c r="F29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$41,prep_table!$O$29)</f>
         <v>5</v>
       </c>
-      <c r="G29" s="98">
+      <c r="G29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$42,prep_table!$O$37)</f>
         <v>5</v>
       </c>
-      <c r="H29" s="98">
+      <c r="H29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$43,prep_table!$O$45)</f>
         <v>5</v>
       </c>
-      <c r="I29" s="98">
+      <c r="I29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$44,prep_table!$O$53)</f>
         <v>5</v>
       </c>
-      <c r="J29" s="98">
+      <c r="J29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$45,prep_table!$O$61)</f>
         <v>5</v>
       </c>
-      <c r="K29" s="98">
+      <c r="K29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$46,prep_table!$O$69)</f>
         <v>5</v>
       </c>
-      <c r="L29" s="98">
+      <c r="L29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$47,prep_table!$O$77)</f>
         <v>5</v>
       </c>
-      <c r="M29" s="98">
+      <c r="M29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$48,prep_table!$O$85)</f>
         <v>5</v>
       </c>
-      <c r="N29" s="98">
+      <c r="N29" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$49,prep_table!$O$93)</f>
         <v>5</v>
       </c>
@@ -8882,51 +8879,51 @@
       <c r="B30" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="98">
+      <c r="C30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$50,prep_table!$O$6)</f>
         <v>5</v>
       </c>
-      <c r="D30" s="98">
+      <c r="D30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$51,prep_table!$O$14)</f>
         <v>5</v>
       </c>
-      <c r="E30" s="98">
+      <c r="E30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$52,prep_table!$O$22)</f>
         <v>5</v>
       </c>
-      <c r="F30" s="98">
+      <c r="F30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$53,prep_table!$O$30)</f>
         <v>5</v>
       </c>
-      <c r="G30" s="98">
+      <c r="G30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$54,prep_table!$O$38)</f>
         <v>5</v>
       </c>
-      <c r="H30" s="98">
+      <c r="H30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$55,prep_table!$O$46)</f>
         <v>5</v>
       </c>
-      <c r="I30" s="98">
+      <c r="I30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$56,prep_table!$O$54)</f>
         <v>5</v>
       </c>
-      <c r="J30" s="98">
+      <c r="J30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$57,prep_table!$O$62)</f>
         <v>5</v>
       </c>
-      <c r="K30" s="98">
+      <c r="K30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$58,prep_table!$O$70)</f>
         <v>5</v>
       </c>
-      <c r="L30" s="98">
+      <c r="L30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$59,prep_table!$O$78)</f>
         <v>5</v>
       </c>
-      <c r="M30" s="98">
+      <c r="M30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$60,prep_table!$O$86)</f>
         <v>5</v>
       </c>
-      <c r="N30" s="98">
+      <c r="N30" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$61,prep_table!$O$94)</f>
         <v>5</v>
       </c>
@@ -8949,51 +8946,51 @@
       <c r="B31" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="98">
+      <c r="C31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$62,prep_table!$O$7)</f>
         <v>5</v>
       </c>
-      <c r="D31" s="98">
+      <c r="D31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$63,prep_table!$O$15)</f>
         <v>5</v>
       </c>
-      <c r="E31" s="98">
+      <c r="E31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$64,prep_table!$O$23)</f>
         <v>5</v>
       </c>
-      <c r="F31" s="98">
+      <c r="F31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$65,prep_table!$O$31)</f>
         <v>5</v>
       </c>
-      <c r="G31" s="98">
+      <c r="G31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$66,prep_table!$O$39)</f>
         <v>5</v>
       </c>
-      <c r="H31" s="98">
+      <c r="H31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$67,prep_table!$O$47)</f>
         <v>5</v>
       </c>
-      <c r="I31" s="98">
+      <c r="I31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$68,prep_table!$O$55)</f>
         <v>5</v>
       </c>
-      <c r="J31" s="98">
+      <c r="J31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$69,prep_table!$O$63)</f>
         <v>5</v>
       </c>
-      <c r="K31" s="98">
+      <c r="K31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$70,prep_table!$O$71)</f>
         <v>5</v>
       </c>
-      <c r="L31" s="98">
+      <c r="L31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$71,prep_table!$O$79)</f>
         <v>5</v>
       </c>
-      <c r="M31" s="98">
+      <c r="M31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$72,prep_table!$O$87)</f>
         <v>5</v>
       </c>
-      <c r="N31" s="98">
+      <c r="N31" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$73,prep_table!$O$95)</f>
         <v>5</v>
       </c>
@@ -9016,51 +9013,51 @@
       <c r="B32" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="98">
+      <c r="C32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$74,prep_table!$O$8)</f>
         <v>5</v>
       </c>
-      <c r="D32" s="98">
+      <c r="D32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$75,prep_table!$O$16)</f>
         <v>5</v>
       </c>
-      <c r="E32" s="98">
+      <c r="E32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$76,prep_table!$O$24)</f>
         <v>5</v>
       </c>
-      <c r="F32" s="98">
+      <c r="F32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$77,prep_table!$O$32)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="98">
+      <c r="G32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$78,prep_table!$O$40)</f>
         <v>5</v>
       </c>
-      <c r="H32" s="98">
+      <c r="H32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$79,prep_table!$O$48)</f>
         <v>5</v>
       </c>
-      <c r="I32" s="98">
+      <c r="I32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$80,prep_table!$O$56)</f>
         <v>5</v>
       </c>
-      <c r="J32" s="98">
+      <c r="J32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$81,prep_table!$O$64)</f>
         <v>5</v>
       </c>
-      <c r="K32" s="98">
+      <c r="K32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$82,prep_table!$O$72)</f>
         <v>5</v>
       </c>
-      <c r="L32" s="98">
+      <c r="L32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$83,prep_table!$O$80)</f>
         <v>5</v>
       </c>
-      <c r="M32" s="98">
+      <c r="M32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$84,prep_table!$O$88)</f>
         <v>5</v>
       </c>
-      <c r="N32" s="98">
+      <c r="N32" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$85,prep_table!$O$96)</f>
         <v>5</v>
       </c>
@@ -9083,51 +9080,51 @@
       <c r="B33" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="98">
+      <c r="C33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$86,prep_table!$O$9)</f>
         <v>5</v>
       </c>
-      <c r="D33" s="98">
+      <c r="D33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$87,prep_table!$O$17)</f>
         <v>5</v>
       </c>
-      <c r="E33" s="98">
+      <c r="E33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$88,prep_table!$O$25)</f>
         <v>5</v>
       </c>
-      <c r="F33" s="98">
+      <c r="F33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$89,prep_table!$O$33)</f>
         <v>5</v>
       </c>
-      <c r="G33" s="98">
+      <c r="G33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$90,prep_table!$O$41)</f>
         <v>5</v>
       </c>
-      <c r="H33" s="98">
+      <c r="H33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$91,prep_table!$O$49)</f>
         <v>5</v>
       </c>
-      <c r="I33" s="98">
+      <c r="I33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$92,prep_table!$O$57)</f>
         <v>5</v>
       </c>
-      <c r="J33" s="98">
+      <c r="J33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$93,prep_table!$O$65)</f>
         <v>5</v>
       </c>
-      <c r="K33" s="98">
+      <c r="K33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$94,prep_table!$O$73)</f>
         <v>5</v>
       </c>
-      <c r="L33" s="98">
+      <c r="L33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$95,prep_table!$O$81)</f>
         <v>5</v>
       </c>
-      <c r="M33" s="98">
+      <c r="M33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$96,prep_table!$O$89)</f>
         <v>5</v>
       </c>
-      <c r="N33" s="98">
+      <c r="N33" s="95">
         <f>IF(ISNUMBER($E$13),prep_table!$O$97,prep_table!$O$97)</f>
         <v>5</v>
       </c>
@@ -9740,22 +9737,22 @@
     </row>
     <row r="43" spans="1:29" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22"/>
-      <c r="B43" s="165" t="s">
+      <c r="B43" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="166"/>
-      <c r="D43" s="166"/>
-      <c r="E43" s="166"/>
-      <c r="F43" s="166"/>
-      <c r="G43" s="166"/>
-      <c r="H43" s="166"/>
-      <c r="I43" s="166"/>
-      <c r="J43" s="166"/>
-      <c r="K43" s="166"/>
-      <c r="L43" s="166"/>
-      <c r="M43" s="166"/>
-      <c r="N43" s="166"/>
-      <c r="O43" s="167"/>
+      <c r="C43" s="124"/>
+      <c r="D43" s="124"/>
+      <c r="E43" s="124"/>
+      <c r="F43" s="124"/>
+      <c r="G43" s="124"/>
+      <c r="H43" s="124"/>
+      <c r="I43" s="124"/>
+      <c r="J43" s="124"/>
+      <c r="K43" s="124"/>
+      <c r="L43" s="124"/>
+      <c r="M43" s="124"/>
+      <c r="N43" s="124"/>
+      <c r="O43" s="125"/>
     </row>
     <row r="44" spans="1:29" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="21"/>
@@ -9766,7 +9763,7 @@
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
       <c r="E44" s="13"/>
-      <c r="N44" s="168" t="str">
+      <c r="N44" s="126" t="str">
         <f>IF(M9="No","Skip this part",IF($M$9=$M$10,"Skip this only for low Input samples", " "))</f>
         <v>Skip this only for low Input samples</v>
       </c>
@@ -9787,7 +9784,7 @@
       <c r="E45" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="N45" s="169"/>
+      <c r="N45" s="127"/>
       <c r="O45" s="28"/>
       <c r="Q45" s="13"/>
     </row>
@@ -9803,7 +9800,7 @@
       <c r="E46" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="N46" s="169"/>
+      <c r="N46" s="127"/>
       <c r="O46" s="28"/>
     </row>
     <row r="47" spans="1:29" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9819,7 +9816,7 @@
       <c r="F47" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="169"/>
+      <c r="N47" s="127"/>
       <c r="O47" s="28"/>
     </row>
     <row r="48" spans="1:29" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9835,7 +9832,7 @@
       <c r="F48" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="N48" s="169"/>
+      <c r="N48" s="127"/>
       <c r="O48" s="28"/>
     </row>
     <row r="49" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9848,28 +9845,28 @@
         <v>14</v>
       </c>
       <c r="F49" s="13"/>
-      <c r="N49" s="169"/>
+      <c r="N49" s="127"/>
       <c r="O49" s="28"/>
     </row>
     <row r="50" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21"/>
-      <c r="B50" s="175" t="str">
+      <c r="B50" s="102" t="str">
         <f>IF(ISNUMBER($E$13),IF($F$13=TRUE,CONCATENATE("Prepare Mastermix (F) according to the following table and pipet ",FIXED($E$13*D54/12*1.1)," µL of F into each well of row B of MM plate"),CONCATENATE("Prepare Mastermix (F) according to the following table and pipet ",FIXED(($G$13+1)*D54*1.1)," µL of F into first ",$H$13," wells and ",FIXED(($G$13)*D54*1.1)," µL into the other wells of MM plate row B")),IF(F12=TRUE,CONCATENATE("Prepare Mastermix (F) according to the following table and pipet ",FIXED(E12*D54/8*1.1)," µL into each well of column 2 of MM plate"),CONCATENATE("Prepare Mastermix (F) according to the following table and pipet ",FIXED((G12+1)*D54*1.1)," µL into first ",H12," wells and ",FIXED((G12)*D54*1.1)," µL into the other wells of MM plate column 2")))</f>
         <v>Prepare Mastermix (F) according to the following table and pipet 0.00 µL into each well of column 2 of MM plate</v>
       </c>
-      <c r="C50" s="176"/>
-      <c r="D50" s="176"/>
-      <c r="E50" s="176"/>
-      <c r="F50" s="176"/>
-      <c r="G50" s="176"/>
-      <c r="H50" s="176"/>
-      <c r="I50" s="176"/>
-      <c r="J50" s="176"/>
-      <c r="K50" s="176"/>
-      <c r="L50" s="176"/>
-      <c r="M50" s="176"/>
-      <c r="N50" s="176"/>
-      <c r="O50" s="176"/>
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="103"/>
+      <c r="J50" s="103"/>
+      <c r="K50" s="103"/>
+      <c r="L50" s="103"/>
+      <c r="M50" s="103"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="103"/>
     </row>
     <row r="51" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="22"/>
@@ -9882,17 +9879,18 @@
         <f>IF(ISNUMBER($E$13),CONCATENATE(" Volume for ",$E$13," samples"),CONCATENATE(" Volume for ",$E$12," samples"))</f>
         <v xml:space="preserve"> Volume for  samples</v>
       </c>
-      <c r="I51" s="150" t="s">
+      <c r="I51" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="J51" s="151"/>
+      <c r="J51" s="110"/>
       <c r="K51" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="L51" s="152" t="s">
-        <v>147</v>
-      </c>
-      <c r="M51" s="152"/>
+      <c r="L51" s="111" t="str">
+        <f>IF(ISNUMBER($E$13),CONCATENATE(" Volume for ",$E$13," samples"),CONCATENATE(" Volume for ",$E$12," samples"))</f>
+        <v xml:space="preserve"> Volume for  samples</v>
+      </c>
+      <c r="M51" s="111"/>
       <c r="N51" s="71"/>
     </row>
     <row r="52" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9911,19 +9909,19 @@
         <v>49</v>
       </c>
       <c r="J52" s="72" t="str">
-        <f>IF(OR($M$10="Yes",$M$11="Yes"), "FS2","")</f>
-        <v>FS2</v>
-      </c>
-      <c r="K52" s="73" t="str">
+        <f>IF(OR($M$10="Yes",$M$11="Yes"), "FS1","")</f>
+        <v>FS1</v>
+      </c>
+      <c r="K52" s="179" t="str">
         <f>IF(OR($M$10="Yes",$M$11="Yes"), "5","")</f>
         <v>5</v>
       </c>
-      <c r="L52" s="135">
+      <c r="L52" s="130">
         <f>IF(ISNUMBER($E$13),IF(OR($M$10="Yes",$M$11="Yes"),K52*$E$13*1.1,""),K52*$E$12*1.1)</f>
         <v>0</v>
       </c>
-      <c r="M52" s="136"/>
-      <c r="N52" s="74" t="s">
+      <c r="M52" s="131"/>
+      <c r="N52" s="73" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9946,16 +9944,16 @@
         <f>IF(OR($M$10="Yes",$M$11="Yes"), "FS2","")</f>
         <v>FS2</v>
       </c>
-      <c r="K53" s="73" t="str">
+      <c r="K53" s="179" t="str">
         <f>IF(OR($M$10="Yes",$M$11="Yes"), "9.5","")</f>
         <v>9.5</v>
       </c>
-      <c r="L53" s="135">
+      <c r="L53" s="130">
         <f t="shared" ref="L53:L54" si="0">IF(ISNUMBER($E$13),IF(OR($M$10="Yes",$M$11="Yes"),K53*$E$13*1.1,""),K53*$E$12*1.1)</f>
         <v>0</v>
       </c>
-      <c r="M53" s="136"/>
-      <c r="N53" s="74" t="s">
+      <c r="M53" s="131"/>
+      <c r="N53" s="73" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9975,20 +9973,20 @@
       <c r="G54" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="J54" s="75" t="str">
+      <c r="J54" s="74" t="str">
         <f>IF(OR($M$10="Yes",$M$11="Yes"), "E1","")</f>
         <v>E1</v>
       </c>
-      <c r="K54" s="76" t="str">
+      <c r="K54" s="180" t="str">
         <f>IF(OR($M$10="Yes",$M$11="Yes"), "0.5","")</f>
         <v>0.5</v>
       </c>
-      <c r="L54" s="135">
+      <c r="L54" s="130">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M54" s="136"/>
-      <c r="N54" s="77" t="s">
+      <c r="M54" s="131"/>
+      <c r="N54" s="75" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10000,17 +9998,16 @@
       <c r="F55" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="J55" s="78"/>
-      <c r="K55" s="79">
-        <f>SUM(K52:K54)</f>
-        <v>0</v>
-      </c>
-      <c r="L55" s="137">
+      <c r="J55" s="76"/>
+      <c r="K55" s="181">
+        <v>15</v>
+      </c>
+      <c r="L55" s="132">
         <f>SUM(L52:L54)</f>
         <v>0</v>
       </c>
-      <c r="M55" s="138"/>
-      <c r="N55" s="80" t="s">
+      <c r="M55" s="133"/>
+      <c r="N55" s="77" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10029,7 +10026,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="13"/>
-      <c r="G57" s="81" t="str">
+      <c r="G57" s="78" t="str">
         <f>IF(OR($M$10="Yes",$M$11="Yes"), "Incubate the low/ultralow input samples for 15 min or 1 hr at 42°C","")</f>
         <v>Incubate the low/ultralow input samples for 15 min or 1 hr at 42°C</v>
       </c>
@@ -10045,22 +10042,22 @@
     </row>
     <row r="59" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22"/>
-      <c r="B59" s="139" t="s">
+      <c r="B59" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="140"/>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
-      <c r="F59" s="140"/>
-      <c r="G59" s="140"/>
-      <c r="H59" s="140"/>
-      <c r="I59" s="140"/>
-      <c r="J59" s="140"/>
-      <c r="K59" s="140"/>
-      <c r="L59" s="140"/>
-      <c r="M59" s="140"/>
-      <c r="N59" s="140"/>
-      <c r="O59" s="141"/>
+      <c r="C59" s="135"/>
+      <c r="D59" s="135"/>
+      <c r="E59" s="135"/>
+      <c r="F59" s="135"/>
+      <c r="G59" s="135"/>
+      <c r="H59" s="135"/>
+      <c r="I59" s="135"/>
+      <c r="J59" s="135"/>
+      <c r="K59" s="135"/>
+      <c r="L59" s="135"/>
+      <c r="M59" s="135"/>
+      <c r="N59" s="135"/>
+      <c r="O59" s="136"/>
     </row>
     <row r="60" spans="1:15" s="13" customFormat="1" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="44"/>
@@ -10096,7 +10093,7 @@
       <c r="D62" s="33">
         <v>5</v>
       </c>
-      <c r="E62" s="82" t="s">
+      <c r="E62" s="79" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10106,7 +10103,7 @@
       <c r="D63" s="36">
         <v>25</v>
       </c>
-      <c r="E63" s="83" t="s">
+      <c r="E63" s="80" t="s">
         <v>49</v>
       </c>
       <c r="F63" s="46" t="s">
@@ -10123,7 +10120,7 @@
         <v>67</v>
       </c>
       <c r="E64" s="13"/>
-      <c r="G64" s="81" t="str">
+      <c r="G64" s="78" t="str">
         <f>IF($M$11="Yes","Incubate: 95°C/5min for ULTRALOW", "")</f>
         <v>Incubate: 95°C/5min for ULTRALOW</v>
       </c>
@@ -10141,22 +10138,22 @@
     </row>
     <row r="66" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22"/>
-      <c r="B66" s="142" t="s">
+      <c r="B66" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="C66" s="143"/>
-      <c r="D66" s="143"/>
-      <c r="E66" s="143"/>
-      <c r="F66" s="143"/>
-      <c r="G66" s="143"/>
-      <c r="H66" s="143"/>
-      <c r="I66" s="143"/>
-      <c r="J66" s="143"/>
-      <c r="K66" s="143"/>
-      <c r="L66" s="143"/>
-      <c r="M66" s="143"/>
-      <c r="N66" s="143"/>
-      <c r="O66" s="144"/>
+      <c r="C66" s="138"/>
+      <c r="D66" s="138"/>
+      <c r="E66" s="138"/>
+      <c r="F66" s="138"/>
+      <c r="G66" s="138"/>
+      <c r="H66" s="138"/>
+      <c r="I66" s="138"/>
+      <c r="J66" s="138"/>
+      <c r="K66" s="138"/>
+      <c r="L66" s="138"/>
+      <c r="M66" s="138"/>
+      <c r="N66" s="138"/>
+      <c r="O66" s="139"/>
     </row>
     <row r="67" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="21"/>
@@ -10167,8 +10164,8 @@
       <c r="G67"/>
       <c r="H67"/>
       <c r="I67"/>
-      <c r="J67" s="84"/>
-      <c r="K67" s="84"/>
+      <c r="J67" s="81"/>
+      <c r="K67" s="81"/>
     </row>
     <row r="68" spans="1:21" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="21"/>
@@ -10197,7 +10194,7 @@
       <c r="D70" s="33">
         <v>10</v>
       </c>
-      <c r="E70" s="82" t="s">
+      <c r="E70" s="79" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10207,7 +10204,7 @@
       <c r="D71" s="36">
         <v>35</v>
       </c>
-      <c r="E71" s="85" t="s">
+      <c r="E71" s="82" t="s">
         <v>49</v>
       </c>
       <c r="F71" s="13" t="s">
@@ -10263,11 +10260,11 @@
       <c r="F76" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="I76" s="145" t="s">
+      <c r="I76" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="J76" s="145"/>
-      <c r="K76" s="145"/>
+      <c r="J76" s="140"/>
+      <c r="K76" s="140"/>
     </row>
     <row r="77" spans="1:21" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C77" s="32" t="s">
@@ -10280,7 +10277,7 @@
         <f>D77*$E$13*1.1</f>
         <v>0</v>
       </c>
-      <c r="F77" s="82" t="s">
+      <c r="F77" s="79" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10294,7 +10291,7 @@
         <f>SUM(E76:E77)</f>
         <v>0</v>
       </c>
-      <c r="F78" s="85" t="s">
+      <c r="F78" s="82" t="s">
         <v>49</v>
       </c>
       <c r="G78" s="14" t="s">
@@ -10309,86 +10306,86 @@
       <c r="D79" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="P79" s="146" t="s">
+      <c r="P79" s="141" t="s">
         <v>122</v>
       </c>
-      <c r="Q79" s="146"/>
+      <c r="Q79" s="141"/>
     </row>
     <row r="80" spans="1:21" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80"/>
-      <c r="B80" s="147" t="s">
+      <c r="B80" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="C80" s="148"/>
-      <c r="D80" s="148"/>
-      <c r="E80" s="148"/>
-      <c r="F80" s="148"/>
-      <c r="G80" s="148"/>
-      <c r="H80" s="148"/>
-      <c r="I80" s="148"/>
-      <c r="J80" s="148"/>
-      <c r="K80" s="148"/>
-      <c r="L80" s="148"/>
-      <c r="M80" s="148"/>
-      <c r="N80" s="148"/>
-      <c r="O80" s="149"/>
-      <c r="P80" s="121" t="s">
+      <c r="C80" s="143"/>
+      <c r="D80" s="143"/>
+      <c r="E80" s="143"/>
+      <c r="F80" s="143"/>
+      <c r="G80" s="143"/>
+      <c r="H80" s="143"/>
+      <c r="I80" s="143"/>
+      <c r="J80" s="143"/>
+      <c r="K80" s="143"/>
+      <c r="L80" s="143"/>
+      <c r="M80" s="143"/>
+      <c r="N80" s="143"/>
+      <c r="O80" s="144"/>
+      <c r="P80" s="129" t="s">
         <v>124</v>
       </c>
-      <c r="Q80" s="121"/>
-      <c r="R80" s="121" t="s">
+      <c r="Q80" s="129"/>
+      <c r="R80" s="129" t="s">
         <v>125</v>
       </c>
-      <c r="S80" s="121"/>
-      <c r="T80" s="121" t="s">
+      <c r="S80" s="129"/>
+      <c r="T80" s="129" t="s">
         <v>126</v>
       </c>
-      <c r="U80" s="121"/>
+      <c r="U80" s="129"/>
     </row>
     <row r="81" spans="1:28" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="21"/>
       <c r="B81" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="P81" s="120" t="s">
+      <c r="P81" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="Q81" s="120"/>
-      <c r="R81" s="120">
+      <c r="Q81" s="145"/>
+      <c r="R81" s="145">
         <v>7</v>
       </c>
-      <c r="S81" s="120"/>
-      <c r="T81" s="121"/>
-      <c r="U81" s="121"/>
+      <c r="S81" s="145"/>
+      <c r="T81" s="129"/>
+      <c r="U81" s="129"/>
     </row>
     <row r="82" spans="1:28" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="21"/>
-      <c r="B82" s="132" t="s">
+      <c r="B82" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="C82" s="133"/>
-      <c r="D82" s="133"/>
-      <c r="E82" s="133"/>
-      <c r="F82" s="133"/>
-      <c r="G82" s="133"/>
-      <c r="H82" s="133"/>
-      <c r="I82" s="133"/>
-      <c r="J82" s="133"/>
-      <c r="K82" s="133"/>
-      <c r="L82" s="133"/>
-      <c r="M82" s="133"/>
-      <c r="N82" s="133"/>
-      <c r="O82" s="134"/>
-      <c r="P82" s="120" t="s">
+      <c r="C82" s="147"/>
+      <c r="D82" s="147"/>
+      <c r="E82" s="147"/>
+      <c r="F82" s="147"/>
+      <c r="G82" s="147"/>
+      <c r="H82" s="147"/>
+      <c r="I82" s="147"/>
+      <c r="J82" s="147"/>
+      <c r="K82" s="147"/>
+      <c r="L82" s="147"/>
+      <c r="M82" s="147"/>
+      <c r="N82" s="147"/>
+      <c r="O82" s="148"/>
+      <c r="P82" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="Q82" s="120"/>
-      <c r="R82" s="120">
+      <c r="Q82" s="145"/>
+      <c r="R82" s="145">
         <v>1</v>
       </c>
-      <c r="S82" s="120"/>
-      <c r="T82" s="121"/>
-      <c r="U82" s="121"/>
+      <c r="S82" s="145"/>
+      <c r="T82" s="129"/>
+      <c r="U82" s="129"/>
     </row>
     <row r="83" spans="1:28" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22"/>
@@ -10399,123 +10396,123 @@
         <v>62</v>
       </c>
       <c r="M83" s="48"/>
-      <c r="P83" s="120" t="s">
+      <c r="P83" s="145" t="s">
         <v>129</v>
       </c>
-      <c r="Q83" s="120"/>
-      <c r="R83" s="120">
-        <v>5</v>
-      </c>
-      <c r="S83" s="120"/>
-      <c r="T83" s="121"/>
-      <c r="U83" s="121"/>
+      <c r="Q83" s="145"/>
+      <c r="R83" s="145">
+        <v>5</v>
+      </c>
+      <c r="S83" s="145"/>
+      <c r="T83" s="129"/>
+      <c r="U83" s="129"/>
     </row>
     <row r="84" spans="1:28" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22"/>
-      <c r="B84" s="128" t="s">
+      <c r="B84" s="154" t="s">
         <v>57</v>
       </c>
-      <c r="C84" s="129"/>
-      <c r="D84" s="129"/>
-      <c r="E84" s="129"/>
-      <c r="F84" s="129"/>
-      <c r="G84" s="129"/>
-      <c r="H84" s="129"/>
-      <c r="I84" s="129"/>
-      <c r="J84" s="129"/>
-      <c r="K84" s="129"/>
-      <c r="L84" s="129"/>
-      <c r="M84" s="129"/>
-      <c r="N84" s="129"/>
-      <c r="O84" s="130"/>
-      <c r="P84" s="131" t="s">
+      <c r="C84" s="155"/>
+      <c r="D84" s="155"/>
+      <c r="E84" s="155"/>
+      <c r="F84" s="155"/>
+      <c r="G84" s="155"/>
+      <c r="H84" s="155"/>
+      <c r="I84" s="155"/>
+      <c r="J84" s="155"/>
+      <c r="K84" s="155"/>
+      <c r="L84" s="155"/>
+      <c r="M84" s="155"/>
+      <c r="N84" s="155"/>
+      <c r="O84" s="156"/>
+      <c r="P84" s="157" t="s">
         <v>130</v>
       </c>
-      <c r="Q84" s="120"/>
-      <c r="R84" s="120">
-        <v>5</v>
-      </c>
-      <c r="S84" s="120"/>
-      <c r="T84" s="121"/>
-      <c r="U84" s="121"/>
+      <c r="Q84" s="145"/>
+      <c r="R84" s="145">
+        <v>5</v>
+      </c>
+      <c r="S84" s="145"/>
+      <c r="T84" s="129"/>
+      <c r="U84" s="129"/>
     </row>
     <row r="85" spans="1:28" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="21"/>
-      <c r="B85" s="125" t="str">
+      <c r="B85" s="151" t="str">
         <f>IF(ISNUMBER($E$12),IF(F12=TRUE,CONCATENATE("Prepare Mastermix (P) according to the following table and pipet ",FIXED(E12*(D89+D90)/8*1.1)," µL of P into each well of column 6 of MM plate"),CONCATENATE("Prepare Mastermix (P) according to the following table and pipet ",FIXED((G12+1)*(D89+D90)*1.1)," µL of P into first ",H12," wells and ",FIXED((G12)*(D89+D90)*1.1)," µL into the other wells of MM plate column 6")),IF(F13=TRUE,CONCATENATE("Prepare Mastermix (P) according to the following table and pipet ",FIXED(E13*(D89+D90)/12*1.1)," µL of P into each well of row F of MM plate"),CONCATENATE("Prepare Mastermix (P) according to the following table and pipet ",FIXED((G13+1)*(D89+D90)*1.1)," µL of P into first ",H13," wells and ",FIXED((G13)*(D89+D90)*1.1)," µL into the other wells of MM plate row F")) )</f>
         <v>Prepare Mastermix (P) according to the following table and pipet 0.00 µL of P into each well of row F of MM plate</v>
       </c>
-      <c r="C85" s="126"/>
-      <c r="D85" s="126"/>
-      <c r="E85" s="126"/>
-      <c r="F85" s="126"/>
-      <c r="G85" s="126"/>
-      <c r="H85" s="126"/>
-      <c r="I85" s="126"/>
-      <c r="J85" s="126"/>
-      <c r="K85" s="126"/>
-      <c r="L85" s="126"/>
-      <c r="M85" s="126"/>
-      <c r="N85" s="126"/>
-      <c r="O85" s="127"/>
-      <c r="P85" s="122" t="s">
+      <c r="C85" s="152"/>
+      <c r="D85" s="152"/>
+      <c r="E85" s="152"/>
+      <c r="F85" s="152"/>
+      <c r="G85" s="152"/>
+      <c r="H85" s="152"/>
+      <c r="I85" s="152"/>
+      <c r="J85" s="152"/>
+      <c r="K85" s="152"/>
+      <c r="L85" s="152"/>
+      <c r="M85" s="152"/>
+      <c r="N85" s="152"/>
+      <c r="O85" s="153"/>
+      <c r="P85" s="158" t="s">
         <v>131</v>
       </c>
-      <c r="Q85" s="122"/>
-      <c r="R85" s="120">
+      <c r="Q85" s="158"/>
+      <c r="R85" s="145">
         <v>0.03</v>
       </c>
-      <c r="S85" s="120"/>
-      <c r="T85" s="121"/>
-      <c r="U85" s="121"/>
+      <c r="S85" s="145"/>
+      <c r="T85" s="129"/>
+      <c r="U85" s="129"/>
     </row>
     <row r="86" spans="1:28" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="21"/>
-      <c r="B86" s="123" t="s">
-        <v>152</v>
-      </c>
-      <c r="C86" s="124"/>
-      <c r="D86" s="124"/>
-      <c r="E86" s="124"/>
-      <c r="F86" s="124"/>
-      <c r="G86" s="124"/>
-      <c r="H86" s="124"/>
-      <c r="I86" s="124"/>
-      <c r="J86" s="124"/>
-      <c r="K86" s="124"/>
-      <c r="L86" s="124"/>
-      <c r="M86" s="124"/>
-      <c r="N86" s="124"/>
-      <c r="O86" s="124"/>
-      <c r="P86" s="122" t="s">
+      <c r="B86" s="149" t="s">
+        <v>151</v>
+      </c>
+      <c r="C86" s="150"/>
+      <c r="D86" s="150"/>
+      <c r="E86" s="150"/>
+      <c r="F86" s="150"/>
+      <c r="G86" s="150"/>
+      <c r="H86" s="150"/>
+      <c r="I86" s="150"/>
+      <c r="J86" s="150"/>
+      <c r="K86" s="150"/>
+      <c r="L86" s="150"/>
+      <c r="M86" s="150"/>
+      <c r="N86" s="150"/>
+      <c r="O86" s="150"/>
+      <c r="P86" s="158" t="s">
         <v>132</v>
       </c>
-      <c r="Q86" s="122"/>
-      <c r="R86" s="120">
+      <c r="Q86" s="158"/>
+      <c r="R86" s="145">
         <v>15.27</v>
       </c>
-      <c r="S86" s="120"/>
-      <c r="T86" s="121"/>
-      <c r="U86" s="121"/>
+      <c r="S86" s="145"/>
+      <c r="T86" s="129"/>
+      <c r="U86" s="129"/>
     </row>
     <row r="87" spans="1:28" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="22"/>
-      <c r="B87" s="86"/>
+      <c r="B87" s="83"/>
       <c r="E87" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="P87" s="120" t="s">
+      <c r="P87" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="Q87" s="120"/>
-      <c r="R87" s="120">
+      <c r="Q87" s="145"/>
+      <c r="R87" s="145">
         <v>1.7</v>
       </c>
-      <c r="S87" s="120"/>
-      <c r="T87" s="121" t="s">
+      <c r="S87" s="145"/>
+      <c r="T87" s="129" t="s">
         <v>133</v>
       </c>
-      <c r="U87" s="121"/>
+      <c r="U87" s="129"/>
     </row>
     <row r="88" spans="1:28" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="22"/>
@@ -10529,16 +10526,16 @@
       <c r="F88" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="P88" s="120" t="s">
+      <c r="P88" s="145" t="s">
         <v>134</v>
       </c>
-      <c r="Q88" s="120"/>
-      <c r="R88" s="120">
+      <c r="Q88" s="145"/>
+      <c r="R88" s="145">
         <v>33.299999999999997</v>
       </c>
-      <c r="S88" s="120"/>
-      <c r="T88" s="121"/>
-      <c r="U88" s="121"/>
+      <c r="S88" s="145"/>
+      <c r="T88" s="129"/>
+      <c r="U88" s="129"/>
     </row>
     <row r="89" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22"/>
@@ -10581,7 +10578,7 @@
         <v>5</v>
       </c>
       <c r="E91" s="33"/>
-      <c r="F91" s="82" t="s">
+      <c r="F91" s="79" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10596,7 +10593,7 @@
         <f>SUM(E89:E90)</f>
         <v>0</v>
       </c>
-      <c r="F92" s="85" t="s">
+      <c r="F92" s="82" t="s">
         <v>49</v>
       </c>
     </row>
@@ -11240,27 +11237,27 @@
     </row>
     <row r="104" spans="1:28" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="22"/>
-      <c r="F104" s="87" t="s">
+      <c r="F104" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="G104" s="101" t="str">
+      <c r="G104" s="168" t="str">
         <f>IF(M83&gt;0,CONCATENATE(M83," cycles"),"___cycles")</f>
         <v>___cycles</v>
       </c>
     </row>
     <row r="105" spans="1:28" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="22"/>
-      <c r="F105" s="88" t="s">
+      <c r="F105" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="G105" s="102"/>
+      <c r="G105" s="169"/>
     </row>
     <row r="106" spans="1:28" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="22"/>
-      <c r="F106" s="89" t="s">
+      <c r="F106" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="G106" s="103"/>
+      <c r="G106" s="170"/>
     </row>
     <row r="107" spans="1:28" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="22"/>
@@ -11275,22 +11272,22 @@
     </row>
     <row r="109" spans="1:28" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109"/>
-      <c r="B109" s="104" t="s">
+      <c r="B109" s="171" t="s">
         <v>138</v>
       </c>
-      <c r="C109" s="105"/>
-      <c r="D109" s="105"/>
-      <c r="E109" s="105"/>
-      <c r="F109" s="105"/>
-      <c r="G109" s="105"/>
-      <c r="H109" s="105"/>
-      <c r="I109" s="105"/>
-      <c r="J109" s="105"/>
-      <c r="K109" s="105"/>
-      <c r="L109" s="105"/>
-      <c r="M109" s="105"/>
-      <c r="N109" s="105"/>
-      <c r="O109" s="106"/>
+      <c r="C109" s="172"/>
+      <c r="D109" s="172"/>
+      <c r="E109" s="172"/>
+      <c r="F109" s="172"/>
+      <c r="G109" s="172"/>
+      <c r="H109" s="172"/>
+      <c r="I109" s="172"/>
+      <c r="J109" s="172"/>
+      <c r="K109" s="172"/>
+      <c r="L109" s="172"/>
+      <c r="M109" s="172"/>
+      <c r="N109" s="172"/>
+      <c r="O109" s="173"/>
     </row>
     <row r="110" spans="1:28" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="21"/>
@@ -11298,26 +11295,26 @@
         <v>139</v>
       </c>
       <c r="F110" s="43"/>
-      <c r="K110" s="90"/>
+      <c r="K110" s="87"/>
     </row>
     <row r="111" spans="1:28" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="91"/>
-      <c r="B111" s="107" t="s">
+      <c r="A111" s="88"/>
+      <c r="B111" s="174" t="s">
         <v>63</v>
       </c>
-      <c r="C111" s="108"/>
-      <c r="D111" s="108"/>
-      <c r="E111" s="108"/>
-      <c r="F111" s="108"/>
-      <c r="G111" s="108"/>
-      <c r="H111" s="108"/>
-      <c r="I111" s="108"/>
-      <c r="J111" s="108"/>
-      <c r="K111" s="108"/>
-      <c r="L111" s="108"/>
-      <c r="M111" s="108"/>
-      <c r="N111" s="108"/>
-      <c r="O111" s="109"/>
+      <c r="C111" s="175"/>
+      <c r="D111" s="175"/>
+      <c r="E111" s="175"/>
+      <c r="F111" s="175"/>
+      <c r="G111" s="175"/>
+      <c r="H111" s="175"/>
+      <c r="I111" s="175"/>
+      <c r="J111" s="175"/>
+      <c r="K111" s="175"/>
+      <c r="L111" s="175"/>
+      <c r="M111" s="175"/>
+      <c r="N111" s="175"/>
+      <c r="O111" s="176"/>
     </row>
     <row r="112" spans="1:28" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="14" t="s">
@@ -11789,16 +11786,16 @@
     </row>
     <row r="122" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="44"/>
-      <c r="B122" s="92" t="s">
+      <c r="B122" s="89" t="s">
         <v>140</v>
       </c>
       <c r="C122" s="13"/>
-      <c r="E122" s="93"/>
+      <c r="E122" s="90"/>
     </row>
     <row r="123" spans="1:15" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="44"/>
       <c r="B123" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C123"/>
       <c r="D123"/>
@@ -11807,260 +11804,314 @@
     <row r="124" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="42"/>
       <c r="B124" s="13"/>
-      <c r="C124" s="92" t="s">
+      <c r="C124" s="89" t="s">
+        <v>152</v>
+      </c>
+      <c r="D124" s="89"/>
+      <c r="E124" s="89"/>
+      <c r="F124" s="89"/>
+      <c r="G124" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="D124" s="92"/>
-      <c r="E124" s="92"/>
-      <c r="F124" s="92"/>
-      <c r="G124" s="13" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="42"/>
       <c r="B125" s="13"/>
-      <c r="C125" s="92" t="s">
+      <c r="C125" s="89" t="s">
+        <v>154</v>
+      </c>
+      <c r="D125" s="13"/>
+      <c r="E125" s="89"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="D125" s="13"/>
-      <c r="E125" s="92"/>
-      <c r="F125" s="92"/>
-      <c r="G125" s="13" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="42"/>
-      <c r="C126" s="100" t="s">
+      <c r="C126" s="167" t="s">
         <v>141</v>
       </c>
-      <c r="D126" s="100"/>
-      <c r="E126" s="100"/>
-      <c r="F126" s="100"/>
-      <c r="G126" s="100"/>
-      <c r="H126" s="100"/>
-      <c r="I126" s="100"/>
-      <c r="J126" s="100"/>
-      <c r="K126" s="99" t="s">
-        <v>160</v>
-      </c>
-      <c r="L126" s="110" t="s">
-        <v>165</v>
-      </c>
-      <c r="M126" s="110"/>
-      <c r="N126" s="110"/>
-      <c r="O126" s="110"/>
+      <c r="D126" s="167"/>
+      <c r="E126" s="167"/>
+      <c r="F126" s="167"/>
+      <c r="G126" s="167"/>
+      <c r="H126" s="167"/>
+      <c r="I126" s="167"/>
+      <c r="J126" s="167"/>
+      <c r="K126" s="96" t="s">
+        <v>159</v>
+      </c>
+      <c r="L126" s="177" t="s">
+        <v>164</v>
+      </c>
+      <c r="M126" s="177"/>
+      <c r="N126" s="177"/>
+      <c r="O126" s="177"/>
     </row>
     <row r="127" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="42"/>
-      <c r="C127" s="100" t="s">
+      <c r="C127" s="167" t="s">
         <v>142</v>
       </c>
-      <c r="D127" s="100"/>
-      <c r="E127" s="100"/>
-      <c r="F127" s="100"/>
-      <c r="G127" s="100"/>
-      <c r="H127" s="100"/>
-      <c r="I127" s="100"/>
-      <c r="J127" s="100"/>
+      <c r="D127" s="167"/>
+      <c r="E127" s="167"/>
+      <c r="F127" s="167"/>
+      <c r="G127" s="167"/>
+      <c r="H127" s="167"/>
+      <c r="I127" s="167"/>
+      <c r="J127" s="167"/>
       <c r="K127" s="30">
         <v>191.96</v>
       </c>
-      <c r="L127" s="111" t="s">
-        <v>161</v>
-      </c>
-      <c r="M127" s="111"/>
-      <c r="N127" s="111"/>
-      <c r="O127" s="111"/>
+      <c r="L127" s="178" t="s">
+        <v>160</v>
+      </c>
+      <c r="M127" s="178"/>
+      <c r="N127" s="178"/>
+      <c r="O127" s="178"/>
     </row>
     <row r="128" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="42"/>
-      <c r="C128" s="100" t="s">
+      <c r="C128" s="167" t="s">
         <v>143</v>
       </c>
-      <c r="D128" s="100"/>
-      <c r="E128" s="100"/>
-      <c r="F128" s="100"/>
-      <c r="G128" s="100"/>
-      <c r="H128" s="100"/>
-      <c r="I128" s="100"/>
-      <c r="J128" s="100"/>
+      <c r="D128" s="167"/>
+      <c r="E128" s="167"/>
+      <c r="F128" s="167"/>
+      <c r="G128" s="167"/>
+      <c r="H128" s="167"/>
+      <c r="I128" s="167"/>
+      <c r="J128" s="167"/>
       <c r="K128" s="30">
         <v>194.96</v>
       </c>
-      <c r="L128" s="111" t="s">
-        <v>162</v>
-      </c>
-      <c r="M128" s="111"/>
-      <c r="N128" s="111"/>
-      <c r="O128" s="111"/>
+      <c r="L128" s="178" t="s">
+        <v>161</v>
+      </c>
+      <c r="M128" s="178"/>
+      <c r="N128" s="178"/>
+      <c r="O128" s="178"/>
     </row>
     <row r="129" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="42"/>
-      <c r="C129" s="100" t="s">
+      <c r="C129" s="167" t="s">
         <v>144</v>
       </c>
-      <c r="D129" s="100"/>
-      <c r="E129" s="100"/>
-      <c r="F129" s="100"/>
-      <c r="G129" s="100"/>
-      <c r="H129" s="100"/>
-      <c r="I129" s="100"/>
-      <c r="J129" s="100"/>
+      <c r="D129" s="167"/>
+      <c r="E129" s="167"/>
+      <c r="F129" s="167"/>
+      <c r="G129" s="167"/>
+      <c r="H129" s="167"/>
+      <c r="I129" s="167"/>
+      <c r="J129" s="167"/>
       <c r="K129" s="30">
         <v>195.96</v>
       </c>
-      <c r="L129" s="111" t="s">
-        <v>163</v>
-      </c>
-      <c r="M129" s="111"/>
-      <c r="N129" s="111"/>
-      <c r="O129" s="111"/>
+      <c r="L129" s="178" t="s">
+        <v>162</v>
+      </c>
+      <c r="M129" s="178"/>
+      <c r="N129" s="178"/>
+      <c r="O129" s="178"/>
     </row>
     <row r="130" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="42"/>
-      <c r="C130" s="100" t="s">
+      <c r="C130" s="167" t="s">
         <v>145</v>
       </c>
-      <c r="D130" s="100"/>
-      <c r="E130" s="100"/>
-      <c r="F130" s="100"/>
-      <c r="G130" s="100"/>
-      <c r="H130" s="100"/>
-      <c r="I130" s="100"/>
-      <c r="J130" s="100"/>
+      <c r="D130" s="167"/>
+      <c r="E130" s="167"/>
+      <c r="F130" s="167"/>
+      <c r="G130" s="167"/>
+      <c r="H130" s="167"/>
+      <c r="I130" s="167"/>
+      <c r="J130" s="167"/>
       <c r="K130" s="30">
         <v>196.96</v>
       </c>
-      <c r="L130" s="111" t="s">
-        <v>164</v>
-      </c>
-      <c r="M130" s="111"/>
-      <c r="N130" s="111"/>
-      <c r="O130" s="111"/>
+      <c r="L130" s="178" t="s">
+        <v>163</v>
+      </c>
+      <c r="M130" s="178"/>
+      <c r="N130" s="178"/>
+      <c r="O130" s="178"/>
     </row>
     <row r="133" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C133" s="119" t="s">
+      <c r="C133" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="D133" s="119"/>
-      <c r="E133" s="119"/>
-      <c r="F133" s="112" t="s">
+      <c r="D133" s="159"/>
+      <c r="E133" s="159"/>
+      <c r="F133" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="G133" s="113"/>
-      <c r="H133" s="113"/>
-      <c r="I133" s="114"/>
+      <c r="G133" s="161"/>
+      <c r="H133" s="161"/>
+      <c r="I133" s="162"/>
     </row>
     <row r="134" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C134" s="118" t="s">
+      <c r="C134" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="D134" s="118"/>
-      <c r="E134" s="118"/>
-      <c r="F134" s="112" t="s">
+      <c r="D134" s="163"/>
+      <c r="E134" s="163"/>
+      <c r="F134" s="160" t="s">
         <v>69</v>
       </c>
-      <c r="G134" s="113"/>
-      <c r="H134" s="113"/>
-      <c r="I134" s="114"/>
+      <c r="G134" s="161"/>
+      <c r="H134" s="161"/>
+      <c r="I134" s="162"/>
     </row>
     <row r="135" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="118" t="s">
+      <c r="C135" s="163" t="s">
         <v>74</v>
       </c>
-      <c r="D135" s="118"/>
-      <c r="E135" s="118"/>
-      <c r="F135" s="112" t="s">
+      <c r="D135" s="163"/>
+      <c r="E135" s="163"/>
+      <c r="F135" s="160" t="s">
         <v>70</v>
       </c>
-      <c r="G135" s="113"/>
-      <c r="H135" s="113"/>
-      <c r="I135" s="114"/>
+      <c r="G135" s="161"/>
+      <c r="H135" s="161"/>
+      <c r="I135" s="162"/>
     </row>
     <row r="136" spans="1:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="112" t="s">
+      <c r="C136" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="D136" s="113"/>
-      <c r="E136" s="114"/>
-      <c r="F136" s="112" t="s">
-        <v>158</v>
-      </c>
-      <c r="G136" s="113"/>
-      <c r="H136" s="113"/>
-      <c r="I136" s="114"/>
+      <c r="D136" s="161"/>
+      <c r="E136" s="162"/>
+      <c r="F136" s="160" t="s">
+        <v>157</v>
+      </c>
+      <c r="G136" s="161"/>
+      <c r="H136" s="161"/>
+      <c r="I136" s="162"/>
     </row>
     <row r="137" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C137" s="112" t="s">
+      <c r="C137" s="160" t="s">
         <v>76</v>
       </c>
-      <c r="D137" s="113"/>
-      <c r="E137" s="114"/>
-      <c r="F137" s="112" t="s">
+      <c r="D137" s="161"/>
+      <c r="E137" s="162"/>
+      <c r="F137" s="160" t="s">
         <v>64</v>
       </c>
-      <c r="G137" s="113"/>
-      <c r="H137" s="113"/>
-      <c r="I137" s="114"/>
+      <c r="G137" s="161"/>
+      <c r="H137" s="161"/>
+      <c r="I137" s="162"/>
     </row>
     <row r="138" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C138" s="112" t="s">
+      <c r="C138" s="160" t="s">
         <v>77</v>
       </c>
-      <c r="D138" s="113"/>
-      <c r="E138" s="114"/>
-      <c r="F138" s="112" t="s">
+      <c r="D138" s="161"/>
+      <c r="E138" s="162"/>
+      <c r="F138" s="160" t="s">
         <v>146</v>
       </c>
-      <c r="G138" s="113"/>
-      <c r="H138" s="113"/>
-      <c r="I138" s="114"/>
+      <c r="G138" s="161"/>
+      <c r="H138" s="161"/>
+      <c r="I138" s="162"/>
     </row>
     <row r="139" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C139" s="112" t="s">
+      <c r="C139" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="D139" s="113"/>
-      <c r="E139" s="114"/>
-      <c r="F139" s="112" t="s">
-        <v>157</v>
-      </c>
-      <c r="G139" s="113"/>
-      <c r="H139" s="113"/>
-      <c r="I139" s="114"/>
+      <c r="D139" s="161"/>
+      <c r="E139" s="162"/>
+      <c r="F139" s="160" t="s">
+        <v>156</v>
+      </c>
+      <c r="G139" s="161"/>
+      <c r="H139" s="161"/>
+      <c r="I139" s="162"/>
     </row>
     <row r="140" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C140" s="112" t="s">
+      <c r="C140" s="160" t="s">
         <v>78</v>
       </c>
-      <c r="D140" s="113"/>
-      <c r="E140" s="114"/>
-      <c r="F140" s="115">
+      <c r="D140" s="161"/>
+      <c r="E140" s="162"/>
+      <c r="F140" s="164">
         <v>20240716</v>
       </c>
-      <c r="G140" s="116"/>
-      <c r="H140" s="116"/>
-      <c r="I140" s="117"/>
+      <c r="G140" s="165"/>
+      <c r="H140" s="165"/>
+      <c r="I140" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="B50:O50"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L129:O129"/>
+    <mergeCell ref="L130:O130"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="F140:I140"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="F135:I135"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="F136:I136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="F137:I137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="F138:I138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="F139:I139"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="F133:I133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="F134:I134"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="C128:J128"/>
+    <mergeCell ref="C129:J129"/>
+    <mergeCell ref="C130:J130"/>
+    <mergeCell ref="G104:G106"/>
+    <mergeCell ref="B109:O109"/>
+    <mergeCell ref="B111:O111"/>
+    <mergeCell ref="C126:J126"/>
+    <mergeCell ref="C127:J127"/>
+    <mergeCell ref="L126:O126"/>
+    <mergeCell ref="L127:O127"/>
+    <mergeCell ref="L128:O128"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="T87:U87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="R88:S88"/>
+    <mergeCell ref="T88:U88"/>
+    <mergeCell ref="B86:O86"/>
+    <mergeCell ref="B85:O85"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="R83:S83"/>
+    <mergeCell ref="T83:U83"/>
+    <mergeCell ref="B84:O84"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="R84:S84"/>
+    <mergeCell ref="T84:U84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="R85:S85"/>
+    <mergeCell ref="T85:U85"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="T86:U86"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="T81:U81"/>
+    <mergeCell ref="B82:O82"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="R82:S82"/>
+    <mergeCell ref="T82:U82"/>
+    <mergeCell ref="T80:U80"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="B59:O59"/>
+    <mergeCell ref="B66:O66"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="B80:O80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="R80:S80"/>
     <mergeCell ref="I51:J51"/>
     <mergeCell ref="L51:M51"/>
     <mergeCell ref="A9:F9"/>
@@ -12077,75 +12128,21 @@
     <mergeCell ref="O2:R10"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="G8:I8"/>
-    <mergeCell ref="T80:U80"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="B59:O59"/>
-    <mergeCell ref="B66:O66"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="B80:O80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="T81:U81"/>
-    <mergeCell ref="B82:O82"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="R82:S82"/>
-    <mergeCell ref="T82:U82"/>
-    <mergeCell ref="B86:O86"/>
-    <mergeCell ref="B85:O85"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="R83:S83"/>
-    <mergeCell ref="T83:U83"/>
-    <mergeCell ref="B84:O84"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="R84:S84"/>
-    <mergeCell ref="T84:U84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="R85:S85"/>
-    <mergeCell ref="T85:U85"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="R86:S86"/>
-    <mergeCell ref="T86:U86"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="T87:U87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="R88:S88"/>
-    <mergeCell ref="T88:U88"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="F133:I133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="F134:I134"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="F140:I140"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="F135:I135"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="F136:I136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="F137:I137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="F138:I138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="F139:I139"/>
-    <mergeCell ref="C128:J128"/>
-    <mergeCell ref="C129:J129"/>
-    <mergeCell ref="C130:J130"/>
-    <mergeCell ref="G104:G106"/>
-    <mergeCell ref="B109:O109"/>
-    <mergeCell ref="B111:O111"/>
-    <mergeCell ref="C126:J126"/>
-    <mergeCell ref="C127:J127"/>
-    <mergeCell ref="L126:O126"/>
-    <mergeCell ref="L127:O127"/>
-    <mergeCell ref="L128:O128"/>
-    <mergeCell ref="L129:O129"/>
-    <mergeCell ref="L130:O130"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="B50:O50"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:I5"/>
   </mergeCells>
   <conditionalFormatting sqref="C26:N33">
     <cfRule type="cellIs" dxfId="23" priority="64" operator="equal">
